--- a/research/traditional_assets/database/data/denmark/denmark_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_furn_home_furnishings.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0862625295078759</v>
+        <v>0.08610785194295857</v>
       </c>
       <c r="C2">
-        <v>133.3183394419741</v>
+        <v>132.2866393874596</v>
       </c>
       <c r="D2">
-        <v>129.3883394419741</v>
+        <v>129.7976393874596</v>
       </c>
       <c r="E2">
-        <v>-47</v>
+        <v>-45.559</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="G2">
         <v>3.93</v>
@@ -1445,28 +1445,28 @@
         <v>15.675</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0724823</v>
       </c>
       <c r="N2">
-        <v>15.675</v>
+        <v>15.6025177</v>
       </c>
       <c r="O2">
-        <v>3.4485</v>
+        <v>3.432553894</v>
       </c>
       <c r="P2">
-        <v>12.2265</v>
+        <v>12.169963806</v>
       </c>
       <c r="Q2">
-        <v>16.9265</v>
+        <v>16.869963806</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0862625295078759</v>
+        <v>0.08658132519490765</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9418319906445184</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>216.2596937459214</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08610785194295857</v>
+        <v>0.08595317437804124</v>
       </c>
       <c r="C3">
-        <v>132.2866393874596</v>
+        <v>131.2575370642668</v>
       </c>
       <c r="D3">
-        <v>129.7976393874596</v>
+        <v>130.2095370642668</v>
       </c>
       <c r="E3">
-        <v>-45.559</v>
+        <v>-44.118</v>
       </c>
       <c r="F3">
-        <v>1.441</v>
+        <v>2.882</v>
       </c>
       <c r="G3">
         <v>3.93</v>
@@ -1527,28 +1527,28 @@
         <v>15.675</v>
       </c>
       <c r="M3">
-        <v>0.0724823</v>
+        <v>0.1449646</v>
       </c>
       <c r="N3">
-        <v>15.6025177</v>
+        <v>15.5300354</v>
       </c>
       <c r="O3">
-        <v>3.432553894</v>
+        <v>3.416607788</v>
       </c>
       <c r="P3">
-        <v>12.169963806</v>
+        <v>12.113427612</v>
       </c>
       <c r="Q3">
-        <v>16.869963806</v>
+        <v>16.813427612</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08658132519490765</v>
+        <v>0.08690662691636862</v>
       </c>
       <c r="T3">
-        <v>0.9418319906445184</v>
+        <v>0.9493447324796448</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>216.2596937459214</v>
+        <v>108.1298468729607</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08595317437804124</v>
+        <v>0.08579849681312392</v>
       </c>
       <c r="C4">
-        <v>131.2575370642668</v>
+        <v>130.2310572819184</v>
       </c>
       <c r="D4">
-        <v>130.2095370642668</v>
+        <v>130.6240572819184</v>
       </c>
       <c r="E4">
-        <v>-44.118</v>
+        <v>-42.677</v>
       </c>
       <c r="F4">
-        <v>2.882</v>
+        <v>4.323</v>
       </c>
       <c r="G4">
         <v>3.93</v>
@@ -1609,28 +1609,28 @@
         <v>15.675</v>
       </c>
       <c r="M4">
-        <v>0.1449646</v>
+        <v>0.2174469</v>
       </c>
       <c r="N4">
-        <v>15.5300354</v>
+        <v>15.4575531</v>
       </c>
       <c r="O4">
-        <v>3.416607788</v>
+        <v>3.400661682</v>
       </c>
       <c r="P4">
-        <v>12.113427612</v>
+        <v>12.056891418</v>
       </c>
       <c r="Q4">
-        <v>16.813427612</v>
+        <v>16.756891418</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08690662691636862</v>
+        <v>0.08723863588981848</v>
       </c>
       <c r="T4">
-        <v>0.9493447324796448</v>
+        <v>0.9570123762082788</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.1298468729607</v>
+        <v>72.0865645819738</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08579849681312392</v>
+        <v>0.08564381924820659</v>
       </c>
       <c r="C5">
-        <v>130.2310572819184</v>
+        <v>129.207225166869</v>
       </c>
       <c r="D5">
-        <v>130.6240572819184</v>
+        <v>131.041225166869</v>
       </c>
       <c r="E5">
-        <v>-42.677</v>
+        <v>-41.236</v>
       </c>
       <c r="F5">
-        <v>4.323</v>
+        <v>5.764</v>
       </c>
       <c r="G5">
         <v>3.93</v>
@@ -1691,28 +1691,28 @@
         <v>15.675</v>
       </c>
       <c r="M5">
-        <v>0.2174469</v>
+        <v>0.2899292</v>
       </c>
       <c r="N5">
-        <v>15.4575531</v>
+        <v>15.3850708</v>
       </c>
       <c r="O5">
-        <v>3.400661682</v>
+        <v>3.384715576</v>
       </c>
       <c r="P5">
-        <v>12.056891418</v>
+        <v>12.000355224</v>
       </c>
       <c r="Q5">
-        <v>16.756891418</v>
+        <v>16.700355224</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08723863588981848</v>
+        <v>0.08757756171688186</v>
       </c>
       <c r="T5">
-        <v>0.9570123762082788</v>
+        <v>0.9648397625145928</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.0865645819738</v>
+        <v>54.06492343648036</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08564381924820659</v>
+        <v>0.08548914168328926</v>
       </c>
       <c r="C6">
-        <v>129.207225166869</v>
+        <v>128.1860661675824</v>
       </c>
       <c r="D6">
-        <v>131.041225166869</v>
+        <v>131.4610661675824</v>
       </c>
       <c r="E6">
-        <v>-41.236</v>
+        <v>-39.795</v>
       </c>
       <c r="F6">
-        <v>5.764</v>
+        <v>7.205</v>
       </c>
       <c r="G6">
         <v>3.93</v>
@@ -1773,28 +1773,28 @@
         <v>15.675</v>
       </c>
       <c r="M6">
-        <v>0.2899292</v>
+        <v>0.3624115</v>
       </c>
       <c r="N6">
-        <v>15.3850708</v>
+        <v>15.3125885</v>
       </c>
       <c r="O6">
-        <v>3.384715576</v>
+        <v>3.36876947</v>
       </c>
       <c r="P6">
-        <v>12.000355224</v>
+        <v>11.94381903</v>
       </c>
       <c r="Q6">
-        <v>16.700355224</v>
+        <v>16.64381903</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08757756171688186</v>
+        <v>0.08792362282451502</v>
       </c>
       <c r="T6">
-        <v>0.9648397625145928</v>
+        <v>0.9728319359010398</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.06492343648036</v>
+        <v>43.25193874918428</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08548914168328926</v>
+        <v>0.08533446411837194</v>
       </c>
       <c r="C7">
-        <v>128.1860661675824</v>
+        <v>127.1676060597064</v>
       </c>
       <c r="D7">
-        <v>131.4610661675824</v>
+        <v>131.8836060597064</v>
       </c>
       <c r="E7">
-        <v>-39.795</v>
+        <v>-38.354</v>
       </c>
       <c r="F7">
-        <v>7.205</v>
+        <v>8.646000000000001</v>
       </c>
       <c r="G7">
         <v>3.93</v>
@@ -1855,28 +1855,28 @@
         <v>15.675</v>
       </c>
       <c r="M7">
-        <v>0.3624115</v>
+        <v>0.4348938</v>
       </c>
       <c r="N7">
-        <v>15.3125885</v>
+        <v>15.2401062</v>
       </c>
       <c r="O7">
-        <v>3.36876947</v>
+        <v>3.352823364</v>
       </c>
       <c r="P7">
-        <v>11.94381903</v>
+        <v>11.887282836</v>
       </c>
       <c r="Q7">
-        <v>16.64381903</v>
+        <v>16.587282836</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08792362282451502</v>
+        <v>0.08827704693443823</v>
       </c>
       <c r="T7">
-        <v>0.9728319359010398</v>
+        <v>0.9809941555297513</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.25193874918428</v>
+        <v>36.0432822909869</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08533446411837194</v>
+        <v>0.08517978655345462</v>
       </c>
       <c r="C8">
-        <v>127.1676060597064</v>
+        <v>126.1518709513478</v>
       </c>
       <c r="D8">
-        <v>131.8836060597064</v>
+        <v>132.3088709513478</v>
       </c>
       <c r="E8">
-        <v>-38.354</v>
+        <v>-36.913</v>
       </c>
       <c r="F8">
-        <v>8.645999999999999</v>
+        <v>10.087</v>
       </c>
       <c r="G8">
         <v>3.93</v>
@@ -1937,28 +1937,28 @@
         <v>15.675</v>
       </c>
       <c r="M8">
-        <v>0.4348937999999999</v>
+        <v>0.5073760999999999</v>
       </c>
       <c r="N8">
-        <v>15.2401062</v>
+        <v>15.1676239</v>
       </c>
       <c r="O8">
-        <v>3.352823364</v>
+        <v>3.336877258</v>
       </c>
       <c r="P8">
-        <v>11.887282836</v>
+        <v>11.830746642</v>
       </c>
       <c r="Q8">
-        <v>16.587282836</v>
+        <v>16.530746642</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08827704693443823</v>
+        <v>0.08863807156285441</v>
       </c>
       <c r="T8">
-        <v>0.9809941555297513</v>
+        <v>0.9893319067633815</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.04328229098691</v>
+        <v>30.89424196370306</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08517978655345462</v>
+        <v>0.0850251089885373</v>
       </c>
       <c r="C9">
-        <v>126.1518709513478</v>
+        <v>125.1388872884503</v>
       </c>
       <c r="D9">
-        <v>132.3088709513478</v>
+        <v>132.7368872884503</v>
       </c>
       <c r="E9">
-        <v>-36.913</v>
+        <v>-35.472</v>
       </c>
       <c r="F9">
-        <v>10.087</v>
+        <v>11.528</v>
       </c>
       <c r="G9">
         <v>3.93</v>
@@ -2019,28 +2019,28 @@
         <v>15.675</v>
       </c>
       <c r="M9">
-        <v>0.5073761</v>
+        <v>0.5798584</v>
       </c>
       <c r="N9">
-        <v>15.1676239</v>
+        <v>15.0951416</v>
       </c>
       <c r="O9">
-        <v>3.336877258</v>
+        <v>3.320931152</v>
       </c>
       <c r="P9">
-        <v>11.830746642</v>
+        <v>11.774210448</v>
       </c>
       <c r="Q9">
-        <v>16.530746642</v>
+        <v>16.474210448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08863807156285443</v>
+        <v>0.08900694455275793</v>
       </c>
       <c r="T9">
-        <v>0.9893319067633817</v>
+        <v>0.9978509134586124</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.89424196370306</v>
+        <v>27.03246171824017</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0850251089885373</v>
+        <v>0.08487043142361997</v>
       </c>
       <c r="C10">
-        <v>125.1388872884503</v>
+        <v>124.1286818602763</v>
       </c>
       <c r="D10">
-        <v>132.7368872884503</v>
+        <v>133.1676818602763</v>
       </c>
       <c r="E10">
-        <v>-35.472</v>
+        <v>-34.031</v>
       </c>
       <c r="F10">
-        <v>11.528</v>
+        <v>12.969</v>
       </c>
       <c r="G10">
         <v>3.93</v>
@@ -2101,28 +2101,28 @@
         <v>15.675</v>
       </c>
       <c r="M10">
-        <v>0.5798584</v>
+        <v>0.6523406999999999</v>
       </c>
       <c r="N10">
-        <v>15.0951416</v>
+        <v>15.0226593</v>
       </c>
       <c r="O10">
-        <v>3.320931152</v>
+        <v>3.304985046</v>
       </c>
       <c r="P10">
-        <v>11.774210448</v>
+        <v>11.717674254</v>
       </c>
       <c r="Q10">
-        <v>16.474210448</v>
+        <v>16.417674254</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08900694455275793</v>
+        <v>0.08938392464134062</v>
       </c>
       <c r="T10">
-        <v>0.9978509134586124</v>
+        <v>1.006557151070222</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.03246171824017</v>
+        <v>24.02885486065794</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08487043142361997</v>
+        <v>0.08471575385870261</v>
       </c>
       <c r="C11">
-        <v>124.1286818602763</v>
+        <v>123.1212818049965</v>
       </c>
       <c r="D11">
-        <v>133.1676818602763</v>
+        <v>133.6012818049965</v>
       </c>
       <c r="E11">
-        <v>-34.031</v>
+        <v>-32.59</v>
       </c>
       <c r="F11">
-        <v>12.969</v>
+        <v>14.41</v>
       </c>
       <c r="G11">
         <v>3.93</v>
@@ -2183,28 +2183,28 @@
         <v>15.675</v>
       </c>
       <c r="M11">
-        <v>0.6523406999999999</v>
+        <v>0.7248229999999999</v>
       </c>
       <c r="N11">
-        <v>15.0226593</v>
+        <v>14.950177</v>
       </c>
       <c r="O11">
-        <v>3.304985046</v>
+        <v>3.28903894</v>
       </c>
       <c r="P11">
-        <v>11.717674254</v>
+        <v>11.66113806</v>
       </c>
       <c r="Q11">
-        <v>16.417674254</v>
+        <v>16.36113806</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08938392464134062</v>
+        <v>0.08976928206522514</v>
       </c>
       <c r="T11">
-        <v>1.006557151070222</v>
+        <v>1.015456860628756</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.02885486065794</v>
+        <v>21.62596937459214</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08471575385870261</v>
+        <v>0.08456107629378531</v>
       </c>
       <c r="C12">
-        <v>123.1212818049965</v>
+        <v>122.1167146153882</v>
       </c>
       <c r="D12">
-        <v>133.6012818049965</v>
+        <v>134.0377146153882</v>
       </c>
       <c r="E12">
-        <v>-32.59</v>
+        <v>-31.149</v>
       </c>
       <c r="F12">
-        <v>14.41</v>
+        <v>15.851</v>
       </c>
       <c r="G12">
         <v>3.93</v>
@@ -2265,28 +2265,28 @@
         <v>15.675</v>
       </c>
       <c r="M12">
-        <v>0.724823</v>
+        <v>0.7973052999999999</v>
       </c>
       <c r="N12">
-        <v>14.950177</v>
+        <v>14.8776947</v>
       </c>
       <c r="O12">
-        <v>3.28903894</v>
+        <v>3.273092834</v>
       </c>
       <c r="P12">
-        <v>11.66113806</v>
+        <v>11.604601866</v>
       </c>
       <c r="Q12">
-        <v>16.36113806</v>
+        <v>16.304601866</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08976928206522514</v>
+        <v>0.09016329920650035</v>
       </c>
       <c r="T12">
-        <v>1.015456860628756</v>
+        <v>1.024556563660516</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.62596937459214</v>
+        <v>19.65997215872013</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08456107629378531</v>
+        <v>0.08440639872886799</v>
       </c>
       <c r="C13">
-        <v>122.1167146153882</v>
+        <v>121.1150081446472</v>
       </c>
       <c r="D13">
-        <v>134.0377146153882</v>
+        <v>134.4770081446472</v>
       </c>
       <c r="E13">
-        <v>-31.149</v>
+        <v>-29.708</v>
       </c>
       <c r="F13">
-        <v>15.851</v>
+        <v>17.292</v>
       </c>
       <c r="G13">
         <v>3.93</v>
@@ -2347,28 +2347,28 @@
         <v>15.675</v>
       </c>
       <c r="M13">
-        <v>0.7973052999999999</v>
+        <v>0.8697875999999999</v>
       </c>
       <c r="N13">
-        <v>14.8776947</v>
+        <v>14.8052124</v>
       </c>
       <c r="O13">
-        <v>3.273092834</v>
+        <v>3.257146727999999</v>
       </c>
       <c r="P13">
-        <v>11.604601866</v>
+        <v>11.548065672</v>
       </c>
       <c r="Q13">
-        <v>16.304601866</v>
+        <v>16.248065672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09016329920650035</v>
+        <v>0.09056627128280452</v>
       </c>
       <c r="T13">
-        <v>1.024556563660516</v>
+        <v>1.033863078124816</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.65997215872013</v>
+        <v>18.02164114549345</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08440639872886799</v>
+        <v>0.08425172116395065</v>
       </c>
       <c r="C14">
-        <v>121.1150081446472</v>
+        <v>120.1161906123126</v>
       </c>
       <c r="D14">
-        <v>134.4770081446472</v>
+        <v>134.9191906123126</v>
       </c>
       <c r="E14">
-        <v>-29.708</v>
+        <v>-28.267</v>
       </c>
       <c r="F14">
-        <v>17.292</v>
+        <v>18.733</v>
       </c>
       <c r="G14">
         <v>3.93</v>
@@ -2429,28 +2429,28 @@
         <v>15.675</v>
       </c>
       <c r="M14">
-        <v>0.8697875999999999</v>
+        <v>0.9422699</v>
       </c>
       <c r="N14">
-        <v>14.8052124</v>
+        <v>14.7327301</v>
       </c>
       <c r="O14">
-        <v>3.257146727999999</v>
+        <v>3.241200622</v>
       </c>
       <c r="P14">
-        <v>11.548065672</v>
+        <v>11.491529478</v>
       </c>
       <c r="Q14">
-        <v>16.248065672</v>
+        <v>16.191529478</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09056627128280452</v>
+        <v>0.09097850708500074</v>
       </c>
       <c r="T14">
-        <v>1.033863078124816</v>
+        <v>1.043383535450364</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.02164114549345</v>
+        <v>16.63536105737857</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08425172116395065</v>
+        <v>0.08409704359903332</v>
       </c>
       <c r="C15">
-        <v>120.1161906123126</v>
+        <v>119.1202906103096</v>
       </c>
       <c r="D15">
-        <v>134.9191906123126</v>
+        <v>135.3642906103096</v>
       </c>
       <c r="E15">
-        <v>-28.267</v>
+        <v>-26.826</v>
       </c>
       <c r="F15">
-        <v>18.733</v>
+        <v>20.174</v>
       </c>
       <c r="G15">
         <v>3.93</v>
@@ -2511,28 +2511,28 @@
         <v>15.675</v>
       </c>
       <c r="M15">
-        <v>0.9422699</v>
+        <v>1.0147522</v>
       </c>
       <c r="N15">
-        <v>14.7327301</v>
+        <v>14.6602478</v>
       </c>
       <c r="O15">
-        <v>3.241200622</v>
+        <v>3.225254516</v>
       </c>
       <c r="P15">
-        <v>11.491529478</v>
+        <v>11.434993284</v>
       </c>
       <c r="Q15">
-        <v>16.191529478</v>
+        <v>16.134993284</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09097850708500074</v>
+        <v>0.09140032976631782</v>
       </c>
       <c r="T15">
-        <v>1.043383535450364</v>
+        <v>1.053125398760227</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.63536105737857</v>
+        <v>15.44712098185153</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08409704359903332</v>
+        <v>0.08394236603411599</v>
       </c>
       <c r="C16">
-        <v>119.1202906103096</v>
+        <v>118.1273371091131</v>
       </c>
       <c r="D16">
-        <v>135.3642906103096</v>
+        <v>135.8123371091131</v>
       </c>
       <c r="E16">
-        <v>-26.826</v>
+        <v>-25.385</v>
       </c>
       <c r="F16">
-        <v>20.174</v>
+        <v>21.615</v>
       </c>
       <c r="G16">
         <v>3.93</v>
@@ -2593,28 +2593,28 @@
         <v>15.675</v>
       </c>
       <c r="M16">
-        <v>1.0147522</v>
+        <v>1.0872345</v>
       </c>
       <c r="N16">
-        <v>14.6602478</v>
+        <v>14.5877655</v>
       </c>
       <c r="O16">
-        <v>3.225254516</v>
+        <v>3.20930841</v>
       </c>
       <c r="P16">
-        <v>11.434993284</v>
+        <v>11.37845709</v>
       </c>
       <c r="Q16">
-        <v>16.134993284</v>
+        <v>16.07845709</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09140032976631782</v>
+        <v>0.09183207768719528</v>
       </c>
       <c r="T16">
-        <v>1.053125398760227</v>
+        <v>1.063096482383263</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.44712098185153</v>
+        <v>14.41731291639476</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08394236603411599</v>
+        <v>0.08378768846919865</v>
       </c>
       <c r="C17">
-        <v>118.1273371091131</v>
+        <v>117.1373594640326</v>
       </c>
       <c r="D17">
-        <v>135.8123371091131</v>
+        <v>136.2633594640326</v>
       </c>
       <c r="E17">
-        <v>-25.385</v>
+        <v>-23.944</v>
       </c>
       <c r="F17">
-        <v>21.615</v>
+        <v>23.056</v>
       </c>
       <c r="G17">
         <v>3.93</v>
@@ -2675,28 +2675,28 @@
         <v>15.675</v>
       </c>
       <c r="M17">
-        <v>1.0872345</v>
+        <v>1.1597168</v>
       </c>
       <c r="N17">
-        <v>14.5877655</v>
+        <v>14.5152832</v>
       </c>
       <c r="O17">
-        <v>3.20930841</v>
+        <v>3.193362304</v>
       </c>
       <c r="P17">
-        <v>11.37845709</v>
+        <v>11.321920896</v>
       </c>
       <c r="Q17">
-        <v>16.07845709</v>
+        <v>16.021920896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09183207768719528</v>
+        <v>0.0922741053204746</v>
       </c>
       <c r="T17">
-        <v>1.063096482383263</v>
+        <v>1.073304972759229</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.41731291639476</v>
+        <v>13.51623085912009</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08378768846919865</v>
+        <v>0.08383191090428134</v>
       </c>
       <c r="C18">
-        <v>117.1373594640326</v>
+        <v>115.5671063197395</v>
       </c>
       <c r="D18">
-        <v>136.2633594640326</v>
+        <v>136.1341063197395</v>
       </c>
       <c r="E18">
-        <v>-23.944</v>
+        <v>-22.503</v>
       </c>
       <c r="F18">
-        <v>23.056</v>
+        <v>24.497</v>
       </c>
       <c r="G18">
         <v>3.93</v>
@@ -2757,45 +2757,45 @@
         <v>15.675</v>
       </c>
       <c r="M18">
-        <v>1.1597168</v>
+        <v>1.2689446</v>
       </c>
       <c r="N18">
-        <v>14.5152832</v>
+        <v>14.4060554</v>
       </c>
       <c r="O18">
-        <v>3.193362304</v>
+        <v>3.169332188</v>
       </c>
       <c r="P18">
-        <v>11.321920896</v>
+        <v>11.236723212</v>
       </c>
       <c r="Q18">
-        <v>16.021920896</v>
+        <v>15.936723212</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0922741053204746</v>
+        <v>0.09272678422202571</v>
       </c>
       <c r="T18">
-        <v>1.073304972759229</v>
+        <v>1.083759450855097</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.51623085912009</v>
+        <v>12.35278514128986</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08383191090428134</v>
+        <v>0.08368893333936402</v>
       </c>
       <c r="C19">
-        <v>115.5671063197395</v>
+        <v>114.5448884667766</v>
       </c>
       <c r="D19">
-        <v>136.1341063197395</v>
+        <v>136.5528884667766</v>
       </c>
       <c r="E19">
-        <v>-22.503</v>
+        <v>-21.062</v>
       </c>
       <c r="F19">
-        <v>24.497</v>
+        <v>25.938</v>
       </c>
       <c r="G19">
         <v>3.93</v>
@@ -2839,28 +2839,28 @@
         <v>15.675</v>
       </c>
       <c r="M19">
-        <v>1.2689446</v>
+        <v>1.3435884</v>
       </c>
       <c r="N19">
-        <v>14.4060554</v>
+        <v>14.3314116</v>
       </c>
       <c r="O19">
-        <v>3.169332188</v>
+        <v>3.152910552</v>
       </c>
       <c r="P19">
-        <v>11.236723212</v>
+        <v>11.178501048</v>
       </c>
       <c r="Q19">
-        <v>15.936723212</v>
+        <v>15.878501048</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09272678422202571</v>
+        <v>0.09319050407239515</v>
       </c>
       <c r="T19">
-        <v>1.083759450855097</v>
+        <v>1.094468916221597</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.35278514128986</v>
+        <v>11.66651930010709</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08368893333936402</v>
+        <v>0.08354595577444669</v>
       </c>
       <c r="C20">
-        <v>114.5448884667766</v>
+        <v>113.5252551191045</v>
       </c>
       <c r="D20">
-        <v>136.5528884667766</v>
+        <v>136.9742551191044</v>
       </c>
       <c r="E20">
-        <v>-21.062</v>
+        <v>-19.621</v>
       </c>
       <c r="F20">
-        <v>25.938</v>
+        <v>27.379</v>
       </c>
       <c r="G20">
         <v>3.93</v>
@@ -2921,28 +2921,28 @@
         <v>15.675</v>
       </c>
       <c r="M20">
-        <v>1.3435884</v>
+        <v>1.4182322</v>
       </c>
       <c r="N20">
-        <v>14.3314116</v>
+        <v>14.2567678</v>
       </c>
       <c r="O20">
-        <v>3.152910552</v>
+        <v>3.136488916</v>
       </c>
       <c r="P20">
-        <v>11.178501048</v>
+        <v>11.120278884</v>
       </c>
       <c r="Q20">
-        <v>15.878501048</v>
+        <v>15.820278884</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09319050407239514</v>
+        <v>0.09366567379561319</v>
       </c>
       <c r="T20">
-        <v>1.094468916221597</v>
+        <v>1.105442812831714</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.66651930010709</v>
+        <v>11.0524919685225</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08354595577444669</v>
+        <v>0.08340297820952935</v>
       </c>
       <c r="C21">
-        <v>113.5252551191045</v>
+        <v>112.5082302761097</v>
       </c>
       <c r="D21">
-        <v>136.9742551191044</v>
+        <v>137.3982302761097</v>
       </c>
       <c r="E21">
-        <v>-19.621</v>
+        <v>-18.18</v>
       </c>
       <c r="F21">
-        <v>27.379</v>
+        <v>28.82</v>
       </c>
       <c r="G21">
         <v>3.93</v>
@@ -3003,28 +3003,28 @@
         <v>15.675</v>
       </c>
       <c r="M21">
-        <v>1.4182322</v>
+        <v>1.492876</v>
       </c>
       <c r="N21">
-        <v>14.2567678</v>
+        <v>14.182124</v>
       </c>
       <c r="O21">
-        <v>3.136488916</v>
+        <v>3.12006728</v>
       </c>
       <c r="P21">
-        <v>11.120278884</v>
+        <v>11.06205672</v>
       </c>
       <c r="Q21">
-        <v>15.820278884</v>
+        <v>15.76205672</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09366567379561319</v>
+        <v>0.09415272276191169</v>
       </c>
       <c r="T21">
-        <v>1.105442812831714</v>
+        <v>1.116691056857083</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.0524919685225</v>
+        <v>10.49986737009638</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08340297820952935</v>
+        <v>0.08326000064461206</v>
       </c>
       <c r="C22">
-        <v>112.5082302761097</v>
+        <v>111.4938382352417</v>
       </c>
       <c r="D22">
-        <v>137.3982302761097</v>
+        <v>137.8248382352417</v>
       </c>
       <c r="E22">
-        <v>-18.18</v>
+        <v>-16.739</v>
       </c>
       <c r="F22">
-        <v>28.82</v>
+        <v>30.261</v>
       </c>
       <c r="G22">
         <v>3.93</v>
@@ -3085,28 +3085,28 @@
         <v>15.675</v>
       </c>
       <c r="M22">
-        <v>1.492876</v>
+        <v>1.5675198</v>
       </c>
       <c r="N22">
-        <v>14.182124</v>
+        <v>14.1074802</v>
       </c>
       <c r="O22">
-        <v>3.12006728</v>
+        <v>3.103645644</v>
       </c>
       <c r="P22">
-        <v>11.06205672</v>
+        <v>11.003834556</v>
       </c>
       <c r="Q22">
-        <v>15.76205672</v>
+        <v>15.703834556</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09415272276191169</v>
+        <v>0.0946521020817874</v>
       </c>
       <c r="T22">
-        <v>1.116691056857083</v>
+        <v>1.128224066553981</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.49986737009638</v>
+        <v>9.999873685806072</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08326000064461203</v>
+        <v>0.0834087430796947</v>
       </c>
       <c r="C23">
-        <v>111.4938382352418</v>
+        <v>109.6090847807101</v>
       </c>
       <c r="D23">
-        <v>137.8248382352418</v>
+        <v>137.3810847807101</v>
       </c>
       <c r="E23">
-        <v>-16.739</v>
+        <v>-15.298</v>
       </c>
       <c r="F23">
-        <v>30.261</v>
+        <v>31.702</v>
       </c>
       <c r="G23">
         <v>3.93</v>
@@ -3167,45 +3167,45 @@
         <v>15.675</v>
       </c>
       <c r="M23">
-        <v>1.5675198</v>
+        <v>1.696057</v>
       </c>
       <c r="N23">
-        <v>14.1074802</v>
+        <v>13.978943</v>
       </c>
       <c r="O23">
-        <v>3.103645644</v>
+        <v>3.07536746</v>
       </c>
       <c r="P23">
-        <v>11.003834556</v>
+        <v>10.90357554</v>
       </c>
       <c r="Q23">
-        <v>15.703834556</v>
+        <v>15.60357554</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09465210208178737</v>
+        <v>0.09516428599960859</v>
       </c>
       <c r="T23">
-        <v>1.128224066553981</v>
+        <v>1.140052794448235</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.999873685806074</v>
+        <v>9.242024295174042</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0834087430796947</v>
+        <v>0.08327902551477738</v>
       </c>
       <c r="C24">
-        <v>109.6090847807101</v>
+        <v>108.5549202233014</v>
       </c>
       <c r="D24">
-        <v>137.3810847807101</v>
+        <v>137.7679202233014</v>
       </c>
       <c r="E24">
-        <v>-15.298</v>
+        <v>-13.857</v>
       </c>
       <c r="F24">
-        <v>31.702</v>
+        <v>33.143</v>
       </c>
       <c r="G24">
         <v>3.93</v>
@@ -3249,28 +3249,28 @@
         <v>15.675</v>
       </c>
       <c r="M24">
-        <v>1.696057</v>
+        <v>1.7731505</v>
       </c>
       <c r="N24">
-        <v>13.978943</v>
+        <v>13.9018495</v>
       </c>
       <c r="O24">
-        <v>3.07536746</v>
+        <v>3.05840689</v>
       </c>
       <c r="P24">
-        <v>10.90357554</v>
+        <v>10.84344261</v>
       </c>
       <c r="Q24">
-        <v>15.60357554</v>
+        <v>15.54344261</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09516428599960859</v>
+        <v>0.09568977339581478</v>
       </c>
       <c r="T24">
-        <v>1.140052794448235</v>
+        <v>1.152188762028055</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.242024295174042</v>
+        <v>8.840197151905604</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08327902551477738</v>
+        <v>0.08314930794986006</v>
       </c>
       <c r="C25">
-        <v>108.5549202233014</v>
+        <v>107.5029403073702</v>
       </c>
       <c r="D25">
-        <v>137.7679202233014</v>
+        <v>138.1569403073702</v>
       </c>
       <c r="E25">
-        <v>-13.857</v>
+        <v>-12.416</v>
       </c>
       <c r="F25">
-        <v>33.143</v>
+        <v>34.584</v>
       </c>
       <c r="G25">
         <v>3.93</v>
@@ -3331,28 +3331,28 @@
         <v>15.675</v>
       </c>
       <c r="M25">
-        <v>1.7731505</v>
+        <v>1.850244</v>
       </c>
       <c r="N25">
-        <v>13.9018495</v>
+        <v>13.824756</v>
       </c>
       <c r="O25">
-        <v>3.05840689</v>
+        <v>3.04144632</v>
       </c>
       <c r="P25">
-        <v>10.84344261</v>
+        <v>10.78330968</v>
       </c>
       <c r="Q25">
-        <v>15.54344261</v>
+        <v>15.48330968</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09568977339581478</v>
+        <v>0.09622908940771059</v>
       </c>
       <c r="T25">
-        <v>1.152188762028055</v>
+        <v>1.164644097175764</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.840197151905604</v>
+        <v>8.471855603909537</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08314930794986006</v>
+        <v>0.08301959038494273</v>
       </c>
       <c r="C26">
-        <v>107.5029403073702</v>
+        <v>106.4531635918673</v>
       </c>
       <c r="D26">
-        <v>138.1569403073702</v>
+        <v>138.5481635918673</v>
       </c>
       <c r="E26">
-        <v>-12.416</v>
+        <v>-10.975</v>
       </c>
       <c r="F26">
-        <v>34.584</v>
+        <v>36.025</v>
       </c>
       <c r="G26">
         <v>3.93</v>
@@ -3413,28 +3413,28 @@
         <v>15.675</v>
       </c>
       <c r="M26">
-        <v>1.850244</v>
+        <v>1.9273375</v>
       </c>
       <c r="N26">
-        <v>13.824756</v>
+        <v>13.7476625</v>
       </c>
       <c r="O26">
-        <v>3.04144632</v>
+        <v>3.02448575</v>
       </c>
       <c r="P26">
-        <v>10.78330968</v>
+        <v>10.72317675</v>
       </c>
       <c r="Q26">
-        <v>15.48330968</v>
+        <v>15.42317675</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09622908940771059</v>
+        <v>0.09678278717992364</v>
       </c>
       <c r="T26">
-        <v>1.164644097175764</v>
+        <v>1.177431574594079</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.471855603909539</v>
+        <v>8.132981379753158</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08301959038494273</v>
+        <v>0.08288987282002541</v>
       </c>
       <c r="C27">
-        <v>106.4531635918673</v>
+        <v>105.4056088465561</v>
       </c>
       <c r="D27">
-        <v>138.5481635918673</v>
+        <v>138.9416088465561</v>
       </c>
       <c r="E27">
-        <v>-10.975</v>
+        <v>-9.533999999999999</v>
       </c>
       <c r="F27">
-        <v>36.025</v>
+        <v>37.466</v>
       </c>
       <c r="G27">
         <v>3.93</v>
@@ -3495,28 +3495,28 @@
         <v>15.675</v>
       </c>
       <c r="M27">
-        <v>1.9273375</v>
+        <v>2.004431</v>
       </c>
       <c r="N27">
-        <v>13.7476625</v>
+        <v>13.670569</v>
       </c>
       <c r="O27">
-        <v>3.02448575</v>
+        <v>3.00752518</v>
       </c>
       <c r="P27">
-        <v>10.72317675</v>
+        <v>10.66304382</v>
       </c>
       <c r="Q27">
-        <v>15.42317675</v>
+        <v>15.36304382</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09678278717992364</v>
+        <v>0.09735144975679108</v>
       </c>
       <c r="T27">
-        <v>1.177431574594079</v>
+        <v>1.190564659510187</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.132981379753158</v>
+        <v>7.820174403608805</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08288987282002541</v>
+        <v>0.08292863525510807</v>
       </c>
       <c r="C28">
-        <v>105.4056088465561</v>
+        <v>103.846804925515</v>
       </c>
       <c r="D28">
-        <v>138.9416088465561</v>
+        <v>138.823804925515</v>
       </c>
       <c r="E28">
-        <v>-9.533999999999999</v>
+        <v>-8.092999999999996</v>
       </c>
       <c r="F28">
-        <v>37.466</v>
+        <v>38.907</v>
       </c>
       <c r="G28">
         <v>3.93</v>
@@ -3577,45 +3577,45 @@
         <v>15.675</v>
       </c>
       <c r="M28">
-        <v>2.004431</v>
+        <v>2.1126501</v>
       </c>
       <c r="N28">
-        <v>13.670569</v>
+        <v>13.5623499</v>
       </c>
       <c r="O28">
-        <v>3.00752518</v>
+        <v>2.983716978</v>
       </c>
       <c r="P28">
-        <v>10.66304382</v>
+        <v>10.578632922</v>
       </c>
       <c r="Q28">
-        <v>15.36304382</v>
+        <v>15.278632922</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09735144975679108</v>
+        <v>0.09793569213028504</v>
       </c>
       <c r="T28">
-        <v>1.190564659510187</v>
+        <v>1.204057554971941</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.820174403608805</v>
+        <v>7.419591157096955</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08292863525510807</v>
+        <v>0.08280515769019076</v>
       </c>
       <c r="C29">
-        <v>103.846804925515</v>
+        <v>102.7817660433703</v>
       </c>
       <c r="D29">
-        <v>138.823804925515</v>
+        <v>139.1997660433703</v>
       </c>
       <c r="E29">
-        <v>-8.092999999999996</v>
+        <v>-6.652000000000001</v>
       </c>
       <c r="F29">
-        <v>38.907</v>
+        <v>40.348</v>
       </c>
       <c r="G29">
         <v>3.93</v>
@@ -3659,28 +3659,28 @@
         <v>15.675</v>
       </c>
       <c r="M29">
-        <v>2.1126501</v>
+        <v>2.1908964</v>
       </c>
       <c r="N29">
-        <v>13.5623499</v>
+        <v>13.4841036</v>
       </c>
       <c r="O29">
-        <v>2.983716978</v>
+        <v>2.966502792</v>
       </c>
       <c r="P29">
-        <v>10.578632922</v>
+        <v>10.517600808</v>
       </c>
       <c r="Q29">
-        <v>15.278632922</v>
+        <v>15.217600808</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09793569213028504</v>
+        <v>0.09853616345859827</v>
       </c>
       <c r="T29">
-        <v>1.204057554971941</v>
+        <v>1.21792525308541</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.419591157096955</v>
+        <v>7.154605758629207</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08280515769019076</v>
+        <v>0.08268168012527341</v>
       </c>
       <c r="C30">
-        <v>102.7817660433703</v>
+        <v>101.7187690386324</v>
       </c>
       <c r="D30">
-        <v>139.1997660433703</v>
+        <v>139.5777690386324</v>
       </c>
       <c r="E30">
-        <v>-6.652000000000001</v>
+        <v>-5.210999999999999</v>
       </c>
       <c r="F30">
-        <v>40.348</v>
+        <v>41.789</v>
       </c>
       <c r="G30">
         <v>3.93</v>
@@ -3741,28 +3741,28 @@
         <v>15.675</v>
       </c>
       <c r="M30">
-        <v>2.1908964</v>
+        <v>2.2691427</v>
       </c>
       <c r="N30">
-        <v>13.4841036</v>
+        <v>13.4058573</v>
       </c>
       <c r="O30">
-        <v>2.966502792</v>
+        <v>2.949288606</v>
       </c>
       <c r="P30">
-        <v>10.517600808</v>
+        <v>10.456568694</v>
       </c>
       <c r="Q30">
-        <v>15.217600808</v>
+        <v>15.156568694</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09853616345859827</v>
+        <v>0.09915354947221608</v>
       </c>
       <c r="T30">
-        <v>1.21792525308541</v>
+        <v>1.232183590582358</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.154605758629207</v>
+        <v>6.9078952152282</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08268168012527341</v>
+        <v>0.08255820256035609</v>
       </c>
       <c r="C31">
-        <v>101.7187690386324</v>
+        <v>100.6578305910152</v>
       </c>
       <c r="D31">
-        <v>139.5777690386324</v>
+        <v>139.9578305910152</v>
       </c>
       <c r="E31">
-        <v>-5.211000000000006</v>
+        <v>-3.770000000000003</v>
       </c>
       <c r="F31">
-        <v>41.78899999999999</v>
+        <v>43.23</v>
       </c>
       <c r="G31">
         <v>3.93</v>
@@ -3823,28 +3823,28 @@
         <v>15.675</v>
       </c>
       <c r="M31">
-        <v>2.2691427</v>
+        <v>2.347389</v>
       </c>
       <c r="N31">
-        <v>13.4058573</v>
+        <v>13.327611</v>
       </c>
       <c r="O31">
-        <v>2.949288606</v>
+        <v>2.93207442</v>
       </c>
       <c r="P31">
-        <v>10.456568694</v>
+        <v>10.39553658</v>
       </c>
       <c r="Q31">
-        <v>15.156568694</v>
+        <v>15.09553658</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09915354947221608</v>
+        <v>0.09978857508622299</v>
       </c>
       <c r="T31">
-        <v>1.232183590582358</v>
+        <v>1.246849309150646</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.9078952152282</v>
+        <v>6.677632041387261</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08255820256035609</v>
+        <v>0.08243472499543876</v>
       </c>
       <c r="C32">
-        <v>100.6578305910152</v>
+        <v>99.59896756240045</v>
       </c>
       <c r="D32">
-        <v>139.9578305910152</v>
+        <v>140.3399675624004</v>
       </c>
       <c r="E32">
-        <v>-3.770000000000003</v>
+        <v>-2.329000000000001</v>
       </c>
       <c r="F32">
-        <v>43.23</v>
+        <v>44.671</v>
       </c>
       <c r="G32">
         <v>3.93</v>
@@ -3905,28 +3905,28 @@
         <v>15.675</v>
       </c>
       <c r="M32">
-        <v>2.347389</v>
+        <v>2.4256353</v>
       </c>
       <c r="N32">
-        <v>13.327611</v>
+        <v>13.2493647</v>
       </c>
       <c r="O32">
-        <v>2.93207442</v>
+        <v>2.914860234</v>
       </c>
       <c r="P32">
-        <v>10.39553658</v>
+        <v>10.334504466</v>
       </c>
       <c r="Q32">
-        <v>15.09553658</v>
+        <v>15.034504466</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09978857508622299</v>
+        <v>0.1004420072397663</v>
       </c>
       <c r="T32">
-        <v>1.246849309150646</v>
+        <v>1.26194012101077</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.677632041387261</v>
+        <v>6.462224556181219</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08243472499543876</v>
+        <v>0.08231124743052144</v>
       </c>
       <c r="C33">
-        <v>99.59896756240045</v>
+        <v>98.54219699933049</v>
       </c>
       <c r="D33">
-        <v>140.3399675624004</v>
+        <v>140.7241969993305</v>
       </c>
       <c r="E33">
-        <v>-2.329000000000001</v>
+        <v>-0.8879999999999981</v>
       </c>
       <c r="F33">
-        <v>44.671</v>
+        <v>46.112</v>
       </c>
       <c r="G33">
         <v>3.93</v>
@@ -3987,28 +3987,28 @@
         <v>15.675</v>
       </c>
       <c r="M33">
-        <v>2.4256353</v>
+        <v>2.5038816</v>
       </c>
       <c r="N33">
-        <v>13.2493647</v>
+        <v>13.1711184</v>
       </c>
       <c r="O33">
-        <v>2.914860234</v>
+        <v>2.897646048</v>
       </c>
       <c r="P33">
-        <v>10.334504466</v>
+        <v>10.273472352</v>
       </c>
       <c r="Q33">
-        <v>15.034504466</v>
+        <v>14.973472352</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1004420072397663</v>
+        <v>0.101114657986061</v>
       </c>
       <c r="T33">
-        <v>1.26194012101077</v>
+        <v>1.277474780278544</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.462224556181219</v>
+        <v>6.260280038800556</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08231124743052144</v>
+        <v>0.08244516986560411</v>
       </c>
       <c r="C34">
-        <v>98.54219699933049</v>
+        <v>96.68456212233508</v>
       </c>
       <c r="D34">
-        <v>140.7241969993305</v>
+        <v>140.3075621223351</v>
       </c>
       <c r="E34">
-        <v>-0.8879999999999981</v>
+        <v>0.5529999999999973</v>
       </c>
       <c r="F34">
-        <v>46.112</v>
+        <v>47.553</v>
       </c>
       <c r="G34">
         <v>3.93</v>
@@ -4069,45 +4069,45 @@
         <v>15.675</v>
       </c>
       <c r="M34">
-        <v>2.5038816</v>
+        <v>2.6296809</v>
       </c>
       <c r="N34">
-        <v>13.1711184</v>
+        <v>13.0453191</v>
       </c>
       <c r="O34">
-        <v>2.897646048</v>
+        <v>2.869970202</v>
       </c>
       <c r="P34">
-        <v>10.273472352</v>
+        <v>10.175348898</v>
       </c>
       <c r="Q34">
-        <v>14.973472352</v>
+        <v>14.875348898</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.101114657986061</v>
+        <v>0.1018073878591106</v>
       </c>
       <c r="T34">
-        <v>1.277474780278544</v>
+        <v>1.29347316071849</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.260280038800556</v>
+        <v>5.960799274162884</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08244516986560411</v>
+        <v>0.08232949230068679</v>
       </c>
       <c r="C35">
-        <v>96.68456212233508</v>
+        <v>95.60329138600835</v>
       </c>
       <c r="D35">
-        <v>140.3075621223351</v>
+        <v>140.6672913860083</v>
       </c>
       <c r="E35">
-        <v>0.5529999999999973</v>
+        <v>1.994</v>
       </c>
       <c r="F35">
-        <v>47.553</v>
+        <v>48.994</v>
       </c>
       <c r="G35">
         <v>3.93</v>
@@ -4151,28 +4151,28 @@
         <v>15.675</v>
       </c>
       <c r="M35">
-        <v>2.6296809</v>
+        <v>2.7093682</v>
       </c>
       <c r="N35">
-        <v>13.0453191</v>
+        <v>12.9656318</v>
       </c>
       <c r="O35">
-        <v>2.869970202</v>
+        <v>2.852438996</v>
       </c>
       <c r="P35">
-        <v>10.175348898</v>
+        <v>10.113192804</v>
       </c>
       <c r="Q35">
-        <v>14.875348898</v>
+        <v>14.813192804</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1018073878591106</v>
+        <v>0.1025211095464951</v>
       </c>
       <c r="T35">
-        <v>1.29347316071849</v>
+        <v>1.309956340565707</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.960799274162884</v>
+        <v>5.785481648452211</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08232949230068679</v>
+        <v>0.08221381473576944</v>
       </c>
       <c r="C36">
-        <v>95.60329138600835</v>
+        <v>94.52386998368701</v>
       </c>
       <c r="D36">
-        <v>140.6672913860083</v>
+        <v>141.028869983687</v>
       </c>
       <c r="E36">
-        <v>1.994</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="F36">
-        <v>48.994</v>
+        <v>50.435</v>
       </c>
       <c r="G36">
         <v>3.93</v>
@@ -4233,28 +4233,28 @@
         <v>15.675</v>
       </c>
       <c r="M36">
-        <v>2.7093682</v>
+        <v>2.7890555</v>
       </c>
       <c r="N36">
-        <v>12.9656318</v>
+        <v>12.8859445</v>
       </c>
       <c r="O36">
-        <v>2.852438996</v>
+        <v>2.83490779</v>
       </c>
       <c r="P36">
-        <v>10.113192804</v>
+        <v>10.05103671</v>
       </c>
       <c r="Q36">
-        <v>14.813192804</v>
+        <v>14.75103671</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1025211095464951</v>
+        <v>0.1032567919011838</v>
       </c>
       <c r="T36">
-        <v>1.309956340565707</v>
+        <v>1.326946695177455</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.785481648452211</v>
+        <v>5.620182172782147</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08221381473576944</v>
+        <v>0.08209813717085213</v>
       </c>
       <c r="C37">
-        <v>94.52386998368701</v>
+        <v>93.44631221299829</v>
       </c>
       <c r="D37">
-        <v>141.028869983687</v>
+        <v>141.3923122129983</v>
       </c>
       <c r="E37">
-        <v>3.435000000000002</v>
+        <v>4.876000000000005</v>
       </c>
       <c r="F37">
-        <v>50.435</v>
+        <v>51.876</v>
       </c>
       <c r="G37">
         <v>3.93</v>
@@ -4315,28 +4315,28 @@
         <v>15.675</v>
       </c>
       <c r="M37">
-        <v>2.7890555</v>
+        <v>2.8687428</v>
       </c>
       <c r="N37">
-        <v>12.8859445</v>
+        <v>12.8062572</v>
       </c>
       <c r="O37">
-        <v>2.83490779</v>
+        <v>2.817376584</v>
       </c>
       <c r="P37">
-        <v>10.05103671</v>
+        <v>9.988880615999999</v>
       </c>
       <c r="Q37">
-        <v>14.75103671</v>
+        <v>14.688880616</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1032567919011838</v>
+        <v>0.1040154643294565</v>
       </c>
       <c r="T37">
-        <v>1.326946695177455</v>
+        <v>1.344467998370819</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.620182172782147</v>
+        <v>5.464066001315977</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08209813717085213</v>
+        <v>0.0819824596059348</v>
       </c>
       <c r="C38">
-        <v>93.44631221299829</v>
+        <v>92.37063251933472</v>
       </c>
       <c r="D38">
-        <v>141.3923122129983</v>
+        <v>141.7576325193347</v>
       </c>
       <c r="E38">
-        <v>4.875999999999998</v>
+        <v>6.317</v>
       </c>
       <c r="F38">
-        <v>51.876</v>
+        <v>53.317</v>
       </c>
       <c r="G38">
         <v>3.93</v>
@@ -4397,28 +4397,28 @@
         <v>15.675</v>
       </c>
       <c r="M38">
-        <v>2.8687428</v>
+        <v>2.9484301</v>
       </c>
       <c r="N38">
-        <v>12.8062572</v>
+        <v>12.7265699</v>
       </c>
       <c r="O38">
-        <v>2.817376584</v>
+        <v>2.799845378</v>
       </c>
       <c r="P38">
-        <v>9.988880615999999</v>
+        <v>9.926724521999999</v>
       </c>
       <c r="Q38">
-        <v>14.688880616</v>
+        <v>14.626724522</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1040154643294565</v>
+        <v>0.1047982215967219</v>
       </c>
       <c r="T38">
-        <v>1.344467998370819</v>
+        <v>1.362545533411591</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.464066001315977</v>
+        <v>5.316388541820951</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0819824596059348</v>
+        <v>0.08186678204101747</v>
       </c>
       <c r="C39">
-        <v>92.37063251933472</v>
+        <v>91.29684549776773</v>
       </c>
       <c r="D39">
-        <v>141.7576325193347</v>
+        <v>142.1248454977677</v>
       </c>
       <c r="E39">
-        <v>6.317</v>
+        <v>7.757999999999996</v>
       </c>
       <c r="F39">
-        <v>53.317</v>
+        <v>54.758</v>
       </c>
       <c r="G39">
         <v>3.93</v>
@@ -4479,28 +4479,28 @@
         <v>15.675</v>
       </c>
       <c r="M39">
-        <v>2.9484301</v>
+        <v>3.0281174</v>
       </c>
       <c r="N39">
-        <v>12.7265699</v>
+        <v>12.6468826</v>
       </c>
       <c r="O39">
-        <v>2.799845378</v>
+        <v>2.782314172</v>
       </c>
       <c r="P39">
-        <v>9.926724521999999</v>
+        <v>9.864568428</v>
       </c>
       <c r="Q39">
-        <v>14.626724522</v>
+        <v>14.564568428</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1047982215967219</v>
+        <v>0.1056062290984153</v>
       </c>
       <c r="T39">
-        <v>1.362545533411591</v>
+        <v>1.381206214744002</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.316388541820951</v>
+        <v>5.176483580194084</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08186678204101747</v>
+        <v>0.08175110447610015</v>
       </c>
       <c r="C40">
-        <v>91.29684549776773</v>
+        <v>90.2249658949914</v>
       </c>
       <c r="D40">
-        <v>142.1248454977677</v>
+        <v>142.4939658949914</v>
       </c>
       <c r="E40">
-        <v>7.757999999999996</v>
+        <v>9.198999999999998</v>
       </c>
       <c r="F40">
-        <v>54.758</v>
+        <v>56.199</v>
       </c>
       <c r="G40">
         <v>3.93</v>
@@ -4561,28 +4561,28 @@
         <v>15.675</v>
       </c>
       <c r="M40">
-        <v>3.0281174</v>
+        <v>3.1078047</v>
       </c>
       <c r="N40">
-        <v>12.6468826</v>
+        <v>12.5671953</v>
       </c>
       <c r="O40">
-        <v>2.782314172</v>
+        <v>2.764782965999999</v>
       </c>
       <c r="P40">
-        <v>9.864568428</v>
+        <v>9.802412334</v>
       </c>
       <c r="Q40">
-        <v>14.564568428</v>
+        <v>14.502412334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1056062290984153</v>
+        <v>0.1064407286493445</v>
       </c>
       <c r="T40">
-        <v>1.381206214744002</v>
+        <v>1.400478721693869</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.176483580194084</v>
+        <v>5.043753231983978</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08175110447610015</v>
+        <v>0.08163542691118282</v>
       </c>
       <c r="C41">
-        <v>90.2249658949914</v>
+        <v>89.15500861129676</v>
       </c>
       <c r="D41">
-        <v>142.4939658949914</v>
+        <v>142.8650086112968</v>
       </c>
       <c r="E41">
-        <v>9.198999999999998</v>
+        <v>10.64</v>
       </c>
       <c r="F41">
-        <v>56.199</v>
+        <v>57.64</v>
       </c>
       <c r="G41">
         <v>3.93</v>
@@ -4643,28 +4643,28 @@
         <v>15.675</v>
       </c>
       <c r="M41">
-        <v>3.1078047</v>
+        <v>3.187492</v>
       </c>
       <c r="N41">
-        <v>12.5671953</v>
+        <v>12.487508</v>
       </c>
       <c r="O41">
-        <v>2.764782965999999</v>
+        <v>2.74725176</v>
       </c>
       <c r="P41">
-        <v>9.802412334</v>
+        <v>9.740256239999999</v>
       </c>
       <c r="Q41">
-        <v>14.502412334</v>
+        <v>14.44025624</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1064407286493445</v>
+        <v>0.1073030448519714</v>
       </c>
       <c r="T41">
-        <v>1.400478721693869</v>
+        <v>1.420393645542064</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.043753231983978</v>
+        <v>4.917659401184379</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08163542691118282</v>
+        <v>0.08151974934626549</v>
       </c>
       <c r="C42">
-        <v>89.15500861129676</v>
+        <v>88.08698870257645</v>
       </c>
       <c r="D42">
-        <v>142.8650086112968</v>
+        <v>143.2379887025764</v>
       </c>
       <c r="E42">
-        <v>10.64</v>
+        <v>12.081</v>
       </c>
       <c r="F42">
-        <v>57.64</v>
+        <v>59.081</v>
       </c>
       <c r="G42">
         <v>3.93</v>
@@ -4725,28 +4725,28 @@
         <v>15.675</v>
       </c>
       <c r="M42">
-        <v>3.187492</v>
+        <v>3.2671793</v>
       </c>
       <c r="N42">
-        <v>12.487508</v>
+        <v>12.4078207</v>
       </c>
       <c r="O42">
-        <v>2.74725176</v>
+        <v>2.729720554</v>
       </c>
       <c r="P42">
-        <v>9.740256239999999</v>
+        <v>9.678100145999998</v>
       </c>
       <c r="Q42">
-        <v>14.44025624</v>
+        <v>14.378100146</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1073030448519714</v>
+        <v>0.1081945921123144</v>
       </c>
       <c r="T42">
-        <v>1.420393645542064</v>
+        <v>1.440983651554605</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.917659401184379</v>
+        <v>4.797716488960369</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08151974934626549</v>
+        <v>0.08140407178134818</v>
       </c>
       <c r="C43">
-        <v>88.08698870257645</v>
+        <v>87.02092138236138</v>
       </c>
       <c r="D43">
-        <v>143.2379887025764</v>
+        <v>143.6129213823614</v>
       </c>
       <c r="E43">
-        <v>12.081</v>
+        <v>13.52200000000001</v>
       </c>
       <c r="F43">
-        <v>59.081</v>
+        <v>60.52200000000001</v>
       </c>
       <c r="G43">
         <v>3.93</v>
@@ -4807,28 +4807,28 @@
         <v>15.675</v>
       </c>
       <c r="M43">
-        <v>3.2671793</v>
+        <v>3.3468666</v>
       </c>
       <c r="N43">
-        <v>12.4078207</v>
+        <v>12.3281334</v>
       </c>
       <c r="O43">
-        <v>2.729720554</v>
+        <v>2.712189348</v>
       </c>
       <c r="P43">
-        <v>9.678100145999998</v>
+        <v>9.615944052</v>
       </c>
       <c r="Q43">
-        <v>14.378100146</v>
+        <v>14.315944052</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1081945921123144</v>
+        <v>0.1091168823816348</v>
       </c>
       <c r="T43">
-        <v>1.440983651554605</v>
+        <v>1.462283657774475</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.797716488960369</v>
+        <v>4.683485143985123</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08140407178134818</v>
+        <v>0.08128839421643086</v>
       </c>
       <c r="C44">
-        <v>87.02092138236139</v>
+        <v>85.95682202388934</v>
       </c>
       <c r="D44">
-        <v>143.6129213823614</v>
+        <v>143.9898220238893</v>
       </c>
       <c r="E44">
-        <v>13.522</v>
+        <v>14.96299999999999</v>
       </c>
       <c r="F44">
-        <v>60.522</v>
+        <v>61.96299999999999</v>
       </c>
       <c r="G44">
         <v>3.93</v>
@@ -4889,28 +4889,28 @@
         <v>15.675</v>
       </c>
       <c r="M44">
-        <v>3.3468666</v>
+        <v>3.4265539</v>
       </c>
       <c r="N44">
-        <v>12.3281334</v>
+        <v>12.2484461</v>
       </c>
       <c r="O44">
-        <v>2.712189348</v>
+        <v>2.694658142</v>
       </c>
       <c r="P44">
-        <v>9.615944052</v>
+        <v>9.553787957999999</v>
       </c>
       <c r="Q44">
-        <v>14.315944052</v>
+        <v>14.253787958</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1091168823816348</v>
+        <v>0.1100715337130366</v>
       </c>
       <c r="T44">
-        <v>1.462283657774475</v>
+        <v>1.484331032633639</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.683485143985123</v>
+        <v>4.574566884822678</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08128839421643086</v>
+        <v>0.08203071665151353</v>
       </c>
       <c r="C45">
-        <v>85.95682202388934</v>
+        <v>82.13100311606217</v>
       </c>
       <c r="D45">
-        <v>143.9898220238893</v>
+        <v>141.6050031160622</v>
       </c>
       <c r="E45">
-        <v>14.96299999999999</v>
+        <v>16.404</v>
       </c>
       <c r="F45">
-        <v>61.96299999999999</v>
+        <v>63.404</v>
       </c>
       <c r="G45">
         <v>3.93</v>
@@ -4971,45 +4971,45 @@
         <v>15.675</v>
       </c>
       <c r="M45">
-        <v>3.4265539</v>
+        <v>3.6647512</v>
       </c>
       <c r="N45">
-        <v>12.2484461</v>
+        <v>12.0102488</v>
       </c>
       <c r="O45">
-        <v>2.694658142</v>
+        <v>2.642254736</v>
       </c>
       <c r="P45">
-        <v>9.553787957999999</v>
+        <v>9.367994063999999</v>
       </c>
       <c r="Q45">
-        <v>14.253787958</v>
+        <v>14.067994064</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1100715337130366</v>
+        <v>0.1110602797348456</v>
       </c>
       <c r="T45">
-        <v>1.484331032633639</v>
+        <v>1.507165813737773</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.574566884822678</v>
+        <v>4.277234427264803</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08203071665151353</v>
+        <v>0.0819345390865962</v>
       </c>
       <c r="C46">
-        <v>82.13100311606217</v>
+        <v>80.99452348263924</v>
       </c>
       <c r="D46">
-        <v>141.6050031160622</v>
+        <v>141.9095234826392</v>
       </c>
       <c r="E46">
-        <v>16.404</v>
+        <v>17.845</v>
       </c>
       <c r="F46">
-        <v>63.404</v>
+        <v>64.845</v>
       </c>
       <c r="G46">
         <v>3.93</v>
@@ -5053,28 +5053,28 @@
         <v>15.675</v>
       </c>
       <c r="M46">
-        <v>3.6647512</v>
+        <v>3.748041</v>
       </c>
       <c r="N46">
-        <v>12.0102488</v>
+        <v>11.926959</v>
       </c>
       <c r="O46">
-        <v>2.642254736</v>
+        <v>2.623930979999999</v>
       </c>
       <c r="P46">
-        <v>9.367994063999999</v>
+        <v>9.303028019999999</v>
       </c>
       <c r="Q46">
-        <v>14.067994064</v>
+        <v>14.00302802</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1110602797348456</v>
+        <v>0.1120849801574476</v>
       </c>
       <c r="T46">
-        <v>1.507165813737773</v>
+        <v>1.530830950518421</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.277234427264803</v>
+        <v>4.182184773325584</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0819345390865962</v>
+        <v>0.08183836152167887</v>
       </c>
       <c r="C47">
-        <v>80.99452348263924</v>
+        <v>79.85935640883196</v>
       </c>
       <c r="D47">
-        <v>141.9095234826392</v>
+        <v>142.215356408832</v>
       </c>
       <c r="E47">
-        <v>17.845</v>
+        <v>19.286</v>
       </c>
       <c r="F47">
-        <v>64.845</v>
+        <v>66.286</v>
       </c>
       <c r="G47">
         <v>3.93</v>
@@ -5135,28 +5135,28 @@
         <v>15.675</v>
       </c>
       <c r="M47">
-        <v>3.748041</v>
+        <v>3.8313308</v>
       </c>
       <c r="N47">
-        <v>11.926959</v>
+        <v>11.8436692</v>
       </c>
       <c r="O47">
-        <v>2.623930979999999</v>
+        <v>2.605607224</v>
       </c>
       <c r="P47">
-        <v>9.303028019999999</v>
+        <v>9.238061975999999</v>
       </c>
       <c r="Q47">
-        <v>14.00302802</v>
+        <v>13.938061976</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1120849801574476</v>
+        <v>0.1131476324475534</v>
       </c>
       <c r="T47">
-        <v>1.530830950518421</v>
+        <v>1.5553725738465</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.182184773325584</v>
+        <v>4.091267713035898</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08183836152167887</v>
+        <v>0.08174218395676154</v>
       </c>
       <c r="C48">
-        <v>79.85935640883196</v>
+        <v>78.72551039916323</v>
       </c>
       <c r="D48">
-        <v>142.215356408832</v>
+        <v>142.5225103991632</v>
       </c>
       <c r="E48">
-        <v>19.286</v>
+        <v>20.727</v>
       </c>
       <c r="F48">
-        <v>66.286</v>
+        <v>67.727</v>
       </c>
       <c r="G48">
         <v>3.93</v>
@@ -5217,28 +5217,28 @@
         <v>15.675</v>
       </c>
       <c r="M48">
-        <v>3.8313308</v>
+        <v>3.914620600000001</v>
       </c>
       <c r="N48">
-        <v>11.8436692</v>
+        <v>11.7603794</v>
       </c>
       <c r="O48">
-        <v>2.605607224</v>
+        <v>2.587283467999999</v>
       </c>
       <c r="P48">
-        <v>9.238061975999999</v>
+        <v>9.173095931999999</v>
       </c>
       <c r="Q48">
-        <v>13.938061976</v>
+        <v>13.873095932</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1131476324475534</v>
+        <v>0.1142503848240784</v>
       </c>
       <c r="T48">
-        <v>1.5553725738465</v>
+        <v>1.580840296168092</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.091267713035898</v>
+        <v>4.004219463822368</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08174218395676154</v>
+        <v>0.08295640639184421</v>
       </c>
       <c r="C49">
-        <v>78.72551039916323</v>
+        <v>73.50152769818314</v>
       </c>
       <c r="D49">
-        <v>142.5225103991632</v>
+        <v>138.7395276981831</v>
       </c>
       <c r="E49">
-        <v>20.727</v>
+        <v>22.16800000000001</v>
       </c>
       <c r="F49">
-        <v>67.727</v>
+        <v>69.16800000000001</v>
       </c>
       <c r="G49">
         <v>3.93</v>
@@ -5299,45 +5299,45 @@
         <v>15.675</v>
       </c>
       <c r="M49">
-        <v>3.914620600000001</v>
+        <v>4.2399984</v>
       </c>
       <c r="N49">
-        <v>11.7603794</v>
+        <v>11.4350016</v>
       </c>
       <c r="O49">
-        <v>2.587283467999999</v>
+        <v>2.515700352</v>
       </c>
       <c r="P49">
-        <v>9.173095931999999</v>
+        <v>8.919301248</v>
       </c>
       <c r="Q49">
-        <v>13.873095932</v>
+        <v>13.619301248</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1142503848240784</v>
+        <v>0.1153955507535465</v>
       </c>
       <c r="T49">
-        <v>1.580840296168092</v>
+        <v>1.607287546271283</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.004219463822368</v>
+        <v>3.696935357334097</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08295640639184421</v>
+        <v>0.08288752882692688</v>
       </c>
       <c r="C50">
-        <v>73.50152769818315</v>
+        <v>72.26973894767094</v>
       </c>
       <c r="D50">
-        <v>138.7395276981831</v>
+        <v>138.9487389476709</v>
       </c>
       <c r="E50">
-        <v>22.16799999999999</v>
+        <v>23.60899999999999</v>
       </c>
       <c r="F50">
-        <v>69.16799999999999</v>
+        <v>70.60899999999999</v>
       </c>
       <c r="G50">
         <v>3.93</v>
@@ -5381,28 +5381,28 @@
         <v>15.675</v>
       </c>
       <c r="M50">
-        <v>4.239998399999999</v>
+        <v>4.3283317</v>
       </c>
       <c r="N50">
-        <v>11.4350016</v>
+        <v>11.3466683</v>
       </c>
       <c r="O50">
-        <v>2.515700352</v>
+        <v>2.496267026</v>
       </c>
       <c r="P50">
-        <v>8.919301248</v>
+        <v>8.850401273999999</v>
       </c>
       <c r="Q50">
-        <v>13.619301248</v>
+        <v>13.550401274</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1153955507535465</v>
+        <v>0.116585625150837</v>
       </c>
       <c r="T50">
-        <v>1.607287546271283</v>
+        <v>1.634771943437345</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.696935357334097</v>
+        <v>3.62148769698034</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08288752882692688</v>
+        <v>0.08281865126200955</v>
       </c>
       <c r="C51">
-        <v>72.26973894767094</v>
+        <v>71.03858210716997</v>
       </c>
       <c r="D51">
-        <v>138.9487389476709</v>
+        <v>139.15858210717</v>
       </c>
       <c r="E51">
-        <v>23.60899999999999</v>
+        <v>25.05</v>
       </c>
       <c r="F51">
-        <v>70.60899999999999</v>
+        <v>72.05</v>
       </c>
       <c r="G51">
         <v>3.93</v>
@@ -5463,28 +5463,28 @@
         <v>15.675</v>
       </c>
       <c r="M51">
-        <v>4.3283317</v>
+        <v>4.416665</v>
       </c>
       <c r="N51">
-        <v>11.3466683</v>
+        <v>11.258335</v>
       </c>
       <c r="O51">
-        <v>2.496267026</v>
+        <v>2.4768337</v>
       </c>
       <c r="P51">
-        <v>8.850401273999999</v>
+        <v>8.781501299999999</v>
       </c>
       <c r="Q51">
-        <v>13.550401274</v>
+        <v>13.4815013</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.116585625150837</v>
+        <v>0.1178233025240191</v>
       </c>
       <c r="T51">
-        <v>1.634771943437345</v>
+        <v>1.663355716490049</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.62148769698034</v>
+        <v>3.549057943040733</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08281865126200955</v>
+        <v>0.08386361369709222</v>
       </c>
       <c r="C52">
-        <v>71.03858210716997</v>
+        <v>66.48059633408066</v>
       </c>
       <c r="D52">
-        <v>139.15858210717</v>
+        <v>136.0415963340807</v>
       </c>
       <c r="E52">
-        <v>25.05</v>
+        <v>26.491</v>
       </c>
       <c r="F52">
-        <v>72.05</v>
+        <v>73.491</v>
       </c>
       <c r="G52">
         <v>3.93</v>
@@ -5545,45 +5545,45 @@
         <v>15.675</v>
       </c>
       <c r="M52">
-        <v>4.416665</v>
+        <v>4.7107731</v>
       </c>
       <c r="N52">
-        <v>11.258335</v>
+        <v>10.9642269</v>
       </c>
       <c r="O52">
-        <v>2.4768337</v>
+        <v>2.412129918</v>
       </c>
       <c r="P52">
-        <v>8.781501299999999</v>
+        <v>8.552096982</v>
       </c>
       <c r="Q52">
-        <v>13.4815013</v>
+        <v>13.252096982</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1178233025240191</v>
+        <v>0.1191114973410045</v>
       </c>
       <c r="T52">
-        <v>1.663355716490049</v>
+        <v>1.693106174157149</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.549057943040733</v>
+        <v>3.327479304830029</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08386361369709222</v>
+        <v>0.0838165761321749</v>
       </c>
       <c r="C53">
-        <v>66.48059633408066</v>
+        <v>65.17689894496088</v>
       </c>
       <c r="D53">
-        <v>136.0415963340807</v>
+        <v>136.1788989449609</v>
       </c>
       <c r="E53">
-        <v>26.491</v>
+        <v>27.932</v>
       </c>
       <c r="F53">
-        <v>73.491</v>
+        <v>74.932</v>
       </c>
       <c r="G53">
         <v>3.93</v>
@@ -5627,28 +5627,28 @@
         <v>15.675</v>
       </c>
       <c r="M53">
-        <v>4.7107731</v>
+        <v>4.803141200000001</v>
       </c>
       <c r="N53">
-        <v>10.9642269</v>
+        <v>10.8718588</v>
       </c>
       <c r="O53">
-        <v>2.412129918</v>
+        <v>2.391808935999999</v>
       </c>
       <c r="P53">
-        <v>8.552096982</v>
+        <v>8.480049863999998</v>
       </c>
       <c r="Q53">
-        <v>13.252096982</v>
+        <v>13.180049864</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1191114973410045</v>
+        <v>0.120453366942031</v>
       </c>
       <c r="T53">
-        <v>1.693106174157149</v>
+        <v>1.724096234227045</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.327479304830029</v>
+        <v>3.263489318198681</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0838165761321749</v>
+        <v>0.08376953856725758</v>
       </c>
       <c r="C54">
-        <v>65.17689894496088</v>
+        <v>63.87347898647174</v>
       </c>
       <c r="D54">
-        <v>136.1788989449609</v>
+        <v>136.3164789864717</v>
       </c>
       <c r="E54">
-        <v>27.932</v>
+        <v>29.373</v>
       </c>
       <c r="F54">
-        <v>74.932</v>
+        <v>76.373</v>
       </c>
       <c r="G54">
         <v>3.93</v>
@@ -5709,28 +5709,28 @@
         <v>15.675</v>
       </c>
       <c r="M54">
-        <v>4.803141200000001</v>
+        <v>4.895509300000001</v>
       </c>
       <c r="N54">
-        <v>10.8718588</v>
+        <v>10.7794907</v>
       </c>
       <c r="O54">
-        <v>2.391808935999999</v>
+        <v>2.371487954</v>
       </c>
       <c r="P54">
-        <v>8.480049863999998</v>
+        <v>8.408002745999999</v>
       </c>
       <c r="Q54">
-        <v>13.180049864</v>
+        <v>13.108002746</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.120453366942031</v>
+        <v>0.1218523373771438</v>
       </c>
       <c r="T54">
-        <v>1.724096234227045</v>
+        <v>1.756405020257362</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.263489318198681</v>
+        <v>3.20191404804399</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08376953856725758</v>
+        <v>0.08372250100234026</v>
       </c>
       <c r="C55">
-        <v>63.87347898647174</v>
+        <v>62.57033730031885</v>
       </c>
       <c r="D55">
-        <v>136.3164789864717</v>
+        <v>136.4543373003189</v>
       </c>
       <c r="E55">
-        <v>29.373</v>
+        <v>30.81400000000001</v>
       </c>
       <c r="F55">
-        <v>76.373</v>
+        <v>77.81400000000001</v>
       </c>
       <c r="G55">
         <v>3.93</v>
@@ -5791,28 +5791,28 @@
         <v>15.675</v>
       </c>
       <c r="M55">
-        <v>4.895509300000001</v>
+        <v>4.9878774</v>
       </c>
       <c r="N55">
-        <v>10.7794907</v>
+        <v>10.6871226</v>
       </c>
       <c r="O55">
-        <v>2.371487954</v>
+        <v>2.351166972</v>
       </c>
       <c r="P55">
-        <v>8.408002745999999</v>
+        <v>8.335955627999999</v>
       </c>
       <c r="Q55">
-        <v>13.108002746</v>
+        <v>13.035955628</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1218523373771438</v>
+        <v>0.1233121326137832</v>
       </c>
       <c r="T55">
-        <v>1.756405020257362</v>
+        <v>1.790118536115084</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.20191404804399</v>
+        <v>3.142619343450582</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08372250100234026</v>
+        <v>0.08367546343742292</v>
       </c>
       <c r="C56">
-        <v>62.57033730031885</v>
+        <v>61.26747473161639</v>
       </c>
       <c r="D56">
-        <v>136.4543373003189</v>
+        <v>136.5924747316164</v>
       </c>
       <c r="E56">
-        <v>30.81400000000001</v>
+        <v>32.25500000000001</v>
       </c>
       <c r="F56">
-        <v>77.81400000000001</v>
+        <v>79.25500000000001</v>
       </c>
       <c r="G56">
         <v>3.93</v>
@@ -5873,28 +5873,28 @@
         <v>15.675</v>
       </c>
       <c r="M56">
-        <v>4.9878774</v>
+        <v>5.080245500000001</v>
       </c>
       <c r="N56">
-        <v>10.6871226</v>
+        <v>10.5947545</v>
       </c>
       <c r="O56">
-        <v>2.351166972</v>
+        <v>2.330845989999999</v>
       </c>
       <c r="P56">
-        <v>8.335955627999999</v>
+        <v>8.263908509999997</v>
       </c>
       <c r="Q56">
-        <v>13.035955628</v>
+        <v>12.96390851</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1233121326137832</v>
+        <v>0.1248368076387176</v>
       </c>
       <c r="T56">
-        <v>1.790118536115084</v>
+        <v>1.825330430455372</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.142619343450582</v>
+        <v>3.085480809933299</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08367546343742292</v>
+        <v>0.08362842587250559</v>
       </c>
       <c r="C57">
-        <v>61.26747473161639</v>
+        <v>59.96489212890393</v>
       </c>
       <c r="D57">
-        <v>136.5924747316164</v>
+        <v>136.7308921289039</v>
       </c>
       <c r="E57">
-        <v>32.25500000000001</v>
+        <v>33.696</v>
       </c>
       <c r="F57">
-        <v>79.25500000000001</v>
+        <v>80.696</v>
       </c>
       <c r="G57">
         <v>3.93</v>
@@ -5955,28 +5955,28 @@
         <v>15.675</v>
       </c>
       <c r="M57">
-        <v>5.080245500000001</v>
+        <v>5.1726136</v>
       </c>
       <c r="N57">
-        <v>10.5947545</v>
+        <v>10.5023864</v>
       </c>
       <c r="O57">
-        <v>2.330845989999999</v>
+        <v>2.310525008</v>
       </c>
       <c r="P57">
-        <v>8.263908509999997</v>
+        <v>8.191861392</v>
       </c>
       <c r="Q57">
-        <v>12.96390851</v>
+        <v>12.891861392</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1248368076387176</v>
+        <v>0.1264307860738763</v>
       </c>
       <c r="T57">
-        <v>1.825330430455372</v>
+        <v>1.862142865447491</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.085480809933299</v>
+        <v>3.030382938327347</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08362842587250559</v>
+        <v>0.08704926830758827</v>
       </c>
       <c r="C58">
-        <v>59.96489212890393</v>
+        <v>49.13883559749408</v>
       </c>
       <c r="D58">
-        <v>136.7308921289039</v>
+        <v>127.3458355974941</v>
       </c>
       <c r="E58">
-        <v>33.696</v>
+        <v>35.137</v>
       </c>
       <c r="F58">
-        <v>80.696</v>
+        <v>82.137</v>
       </c>
       <c r="G58">
         <v>3.93</v>
@@ -6037,45 +6037,45 @@
         <v>15.675</v>
       </c>
       <c r="M58">
-        <v>5.1726136</v>
+        <v>5.9056503</v>
       </c>
       <c r="N58">
-        <v>10.5023864</v>
+        <v>9.769349699999999</v>
       </c>
       <c r="O58">
-        <v>2.310525008</v>
+        <v>2.149256934</v>
       </c>
       <c r="P58">
-        <v>8.191861392</v>
+        <v>7.620092765999999</v>
       </c>
       <c r="Q58">
-        <v>12.891861392</v>
+        <v>12.320092766</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1264307860738763</v>
+        <v>0.128098903040903</v>
       </c>
       <c r="T58">
-        <v>1.862142865447491</v>
+        <v>1.900667506718313</v>
       </c>
       <c r="U58">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.030382938327347</v>
+        <v>2.654237756001232</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08704926830758827</v>
+        <v>0.08706307074267094</v>
       </c>
       <c r="C59">
-        <v>49.13883559749408</v>
+        <v>47.66257762161177</v>
       </c>
       <c r="D59">
-        <v>127.3458355974941</v>
+        <v>127.3105776216118</v>
       </c>
       <c r="E59">
-        <v>35.137</v>
+        <v>36.578</v>
       </c>
       <c r="F59">
-        <v>82.137</v>
+        <v>83.578</v>
       </c>
       <c r="G59">
         <v>3.93</v>
@@ -6119,28 +6119,28 @@
         <v>15.675</v>
       </c>
       <c r="M59">
-        <v>5.9056503</v>
+        <v>6.009258200000001</v>
       </c>
       <c r="N59">
-        <v>9.769349699999999</v>
+        <v>9.665741799999999</v>
       </c>
       <c r="O59">
-        <v>2.149256934</v>
+        <v>2.126463196</v>
       </c>
       <c r="P59">
-        <v>7.620092765999999</v>
+        <v>7.539278604</v>
       </c>
       <c r="Q59">
-        <v>12.320092766</v>
+        <v>12.239278604</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.128098903040903</v>
+        <v>0.1298464541492165</v>
       </c>
       <c r="T59">
-        <v>1.900667506718313</v>
+        <v>1.941026654716317</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.654237756001232</v>
+        <v>2.608475036070176</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08706307074267094</v>
+        <v>0.08707687317775362</v>
       </c>
       <c r="C60">
-        <v>47.66257762161179</v>
+        <v>46.18633916393004</v>
       </c>
       <c r="D60">
-        <v>127.3105776216118</v>
+        <v>127.27533916393</v>
       </c>
       <c r="E60">
-        <v>36.57799999999999</v>
+        <v>38.01899999999999</v>
       </c>
       <c r="F60">
-        <v>83.57799999999999</v>
+        <v>85.01899999999999</v>
       </c>
       <c r="G60">
         <v>3.93</v>
@@ -6201,28 +6201,28 @@
         <v>15.675</v>
       </c>
       <c r="M60">
-        <v>6.0092582</v>
+        <v>6.1128661</v>
       </c>
       <c r="N60">
-        <v>9.665741799999999</v>
+        <v>9.562133899999999</v>
       </c>
       <c r="O60">
-        <v>2.126463196</v>
+        <v>2.103669458</v>
       </c>
       <c r="P60">
-        <v>7.539278604</v>
+        <v>7.458464441999999</v>
       </c>
       <c r="Q60">
-        <v>12.239278604</v>
+        <v>12.158464442</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1298464541492165</v>
+        <v>0.1316792516530576</v>
       </c>
       <c r="T60">
-        <v>1.941026654716317</v>
+        <v>1.983354541641053</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.608475036070176</v>
+        <v>2.564263594780851</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08707687317775362</v>
+        <v>0.08709067561283629</v>
       </c>
       <c r="C61">
-        <v>46.18633916393004</v>
+        <v>44.7101202082459</v>
       </c>
       <c r="D61">
-        <v>127.27533916393</v>
+        <v>127.2401202082459</v>
       </c>
       <c r="E61">
-        <v>38.01899999999999</v>
+        <v>39.45999999999999</v>
       </c>
       <c r="F61">
-        <v>85.01899999999999</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="G61">
         <v>3.93</v>
@@ -6283,28 +6283,28 @@
         <v>15.675</v>
       </c>
       <c r="M61">
-        <v>6.1128661</v>
+        <v>6.216474</v>
       </c>
       <c r="N61">
-        <v>9.562133899999999</v>
+        <v>9.458525999999999</v>
       </c>
       <c r="O61">
-        <v>2.103669458</v>
+        <v>2.08087572</v>
       </c>
       <c r="P61">
-        <v>7.458464441999999</v>
+        <v>7.377650279999999</v>
       </c>
       <c r="Q61">
-        <v>12.158464442</v>
+        <v>12.07765028</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1316792516530576</v>
+        <v>0.1336036890320907</v>
       </c>
       <c r="T61">
-        <v>1.983354541641053</v>
+        <v>2.027798822912025</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.564263594780851</v>
+        <v>2.52152586820117</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08709067561283629</v>
+        <v>0.08896009804791896</v>
       </c>
       <c r="C62">
-        <v>44.7101202082459</v>
+        <v>38.6726034227423</v>
       </c>
       <c r="D62">
-        <v>127.2401202082459</v>
+        <v>122.6436034227423</v>
       </c>
       <c r="E62">
-        <v>39.45999999999999</v>
+        <v>40.901</v>
       </c>
       <c r="F62">
-        <v>86.45999999999999</v>
+        <v>87.901</v>
       </c>
       <c r="G62">
         <v>3.93</v>
@@ -6365,45 +6365,45 @@
         <v>15.675</v>
       </c>
       <c r="M62">
-        <v>6.216474</v>
+        <v>6.6628958</v>
       </c>
       <c r="N62">
-        <v>9.458525999999999</v>
+        <v>9.0121042</v>
       </c>
       <c r="O62">
-        <v>2.08087572</v>
+        <v>1.982662924</v>
       </c>
       <c r="P62">
-        <v>7.377650279999999</v>
+        <v>7.029441276</v>
       </c>
       <c r="Q62">
-        <v>12.07765028</v>
+        <v>11.729441276</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1336036890320907</v>
+        <v>0.1356268155074845</v>
       </c>
       <c r="T62">
-        <v>2.027798822912025</v>
+        <v>2.07452229809433</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.52152586820117</v>
+        <v>2.352580690215807</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08896009804791896</v>
+        <v>0.08900432048300164</v>
       </c>
       <c r="C63">
-        <v>38.6726034227423</v>
+        <v>37.12688721295213</v>
       </c>
       <c r="D63">
-        <v>122.6436034227423</v>
+        <v>122.5388872129521</v>
       </c>
       <c r="E63">
-        <v>40.901</v>
+        <v>42.342</v>
       </c>
       <c r="F63">
-        <v>87.901</v>
+        <v>89.342</v>
       </c>
       <c r="G63">
         <v>3.93</v>
@@ -6447,28 +6447,28 @@
         <v>15.675</v>
       </c>
       <c r="M63">
-        <v>6.6628958</v>
+        <v>6.7721236</v>
       </c>
       <c r="N63">
-        <v>9.0121042</v>
+        <v>8.902876399999998</v>
       </c>
       <c r="O63">
-        <v>1.982662924</v>
+        <v>1.958632808</v>
       </c>
       <c r="P63">
-        <v>7.029441276</v>
+        <v>6.944243591999999</v>
       </c>
       <c r="Q63">
-        <v>11.729441276</v>
+        <v>11.644243592</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1356268155074845</v>
+        <v>0.1377564223236885</v>
       </c>
       <c r="T63">
-        <v>2.07452229809433</v>
+        <v>2.123704903549388</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.352580690215807</v>
+        <v>2.314635840373616</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08900432048300164</v>
+        <v>0.08904854291808431</v>
       </c>
       <c r="C64">
-        <v>37.12688721295213</v>
+        <v>35.58134966930787</v>
       </c>
       <c r="D64">
-        <v>122.5388872129521</v>
+        <v>122.4343496693079</v>
       </c>
       <c r="E64">
-        <v>42.342</v>
+        <v>43.783</v>
       </c>
       <c r="F64">
-        <v>89.342</v>
+        <v>90.783</v>
       </c>
       <c r="G64">
         <v>3.93</v>
@@ -6529,28 +6529,28 @@
         <v>15.675</v>
       </c>
       <c r="M64">
-        <v>6.7721236</v>
+        <v>6.881351400000001</v>
       </c>
       <c r="N64">
-        <v>8.902876399999998</v>
+        <v>8.793648599999997</v>
       </c>
       <c r="O64">
-        <v>1.958632808</v>
+        <v>1.934602691999999</v>
       </c>
       <c r="P64">
-        <v>6.944243591999999</v>
+        <v>6.859045907999998</v>
       </c>
       <c r="Q64">
-        <v>11.644243592</v>
+        <v>11.559045908</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1377564223236885</v>
+        <v>0.1400011430218495</v>
       </c>
       <c r="T64">
-        <v>2.123704903549388</v>
+        <v>2.175546028218232</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.314635840373616</v>
+        <v>2.277895588939114</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08904854291808431</v>
+        <v>0.08909276535316699</v>
       </c>
       <c r="C65">
-        <v>35.58134966930787</v>
+        <v>34.03599033494068</v>
       </c>
       <c r="D65">
-        <v>122.4343496693079</v>
+        <v>122.3299903349407</v>
       </c>
       <c r="E65">
-        <v>43.783</v>
+        <v>45.224</v>
       </c>
       <c r="F65">
-        <v>90.783</v>
+        <v>92.224</v>
       </c>
       <c r="G65">
         <v>3.93</v>
@@ -6611,28 +6611,28 @@
         <v>15.675</v>
       </c>
       <c r="M65">
-        <v>6.881351400000001</v>
+        <v>6.990579200000001</v>
       </c>
       <c r="N65">
-        <v>8.793648599999997</v>
+        <v>8.684420799999998</v>
       </c>
       <c r="O65">
-        <v>1.934602691999999</v>
+        <v>1.910572576</v>
       </c>
       <c r="P65">
-        <v>6.859045907999998</v>
+        <v>6.773848223999998</v>
       </c>
       <c r="Q65">
-        <v>11.559045908</v>
+        <v>11.473848224</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1400011430218495</v>
+        <v>0.1423705704254638</v>
       </c>
       <c r="T65">
-        <v>2.175546028218232</v>
+        <v>2.230267215368679</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.277895588939114</v>
+        <v>2.24230347036194</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08909276535316699</v>
+        <v>0.08913698778824966</v>
       </c>
       <c r="C66">
-        <v>34.03599033494068</v>
+        <v>32.49080875453807</v>
       </c>
       <c r="D66">
-        <v>122.3299903349407</v>
+        <v>122.2258087545381</v>
       </c>
       <c r="E66">
-        <v>45.224</v>
+        <v>46.66500000000001</v>
       </c>
       <c r="F66">
-        <v>92.224</v>
+        <v>93.66500000000001</v>
       </c>
       <c r="G66">
         <v>3.93</v>
@@ -6693,28 +6693,28 @@
         <v>15.675</v>
       </c>
       <c r="M66">
-        <v>6.990579200000001</v>
+        <v>7.099807000000001</v>
       </c>
       <c r="N66">
-        <v>8.684420799999998</v>
+        <v>8.575192999999999</v>
       </c>
       <c r="O66">
-        <v>1.910572576</v>
+        <v>1.88654246</v>
       </c>
       <c r="P66">
-        <v>6.773848223999998</v>
+        <v>6.688650539999999</v>
       </c>
       <c r="Q66">
-        <v>11.473848224</v>
+        <v>11.38865054</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1423705704254638</v>
+        <v>0.1448753936807133</v>
       </c>
       <c r="T66">
-        <v>2.230267215368679</v>
+        <v>2.288115327499152</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.24230347036194</v>
+        <v>2.207806493894834</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08913698778824966</v>
+        <v>0.08918121022333232</v>
       </c>
       <c r="C67">
-        <v>32.49080875453807</v>
+        <v>30.94580447433731</v>
       </c>
       <c r="D67">
-        <v>122.2258087545381</v>
+        <v>122.1218044743373</v>
       </c>
       <c r="E67">
-        <v>46.66500000000001</v>
+        <v>48.10599999999999</v>
       </c>
       <c r="F67">
-        <v>93.66500000000001</v>
+        <v>95.10599999999999</v>
       </c>
       <c r="G67">
         <v>3.93</v>
@@ -6775,28 +6775,28 @@
         <v>15.675</v>
       </c>
       <c r="M67">
-        <v>7.099807000000001</v>
+        <v>7.2090348</v>
       </c>
       <c r="N67">
-        <v>8.575192999999999</v>
+        <v>8.465965199999999</v>
       </c>
       <c r="O67">
-        <v>1.88654246</v>
+        <v>1.862512344</v>
       </c>
       <c r="P67">
-        <v>6.688650539999999</v>
+        <v>6.603452856</v>
       </c>
       <c r="Q67">
-        <v>11.38865054</v>
+        <v>11.303452856</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1448753936807133</v>
+        <v>0.1475275594803892</v>
       </c>
       <c r="T67">
-        <v>2.288115327499152</v>
+        <v>2.349366269754947</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.207806493894834</v>
+        <v>2.174354880350973</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08918121022333232</v>
+        <v>0.08922543265841501</v>
       </c>
       <c r="C68">
-        <v>30.94580447433731</v>
+        <v>29.40097704211868</v>
       </c>
       <c r="D68">
-        <v>122.1218044743373</v>
+        <v>122.0179770421187</v>
       </c>
       <c r="E68">
-        <v>48.10599999999999</v>
+        <v>49.547</v>
       </c>
       <c r="F68">
-        <v>95.10599999999999</v>
+        <v>96.547</v>
       </c>
       <c r="G68">
         <v>3.93</v>
@@ -6857,28 +6857,28 @@
         <v>15.675</v>
       </c>
       <c r="M68">
-        <v>7.2090348</v>
+        <v>7.318262600000001</v>
       </c>
       <c r="N68">
-        <v>8.465965199999999</v>
+        <v>8.356737399999998</v>
       </c>
       <c r="O68">
-        <v>1.862512344</v>
+        <v>1.838482228</v>
       </c>
       <c r="P68">
-        <v>6.603452856</v>
+        <v>6.518255171999998</v>
       </c>
       <c r="Q68">
-        <v>11.303452856</v>
+        <v>11.218255172</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1475275594803892</v>
+        <v>0.1503404626012576</v>
       </c>
       <c r="T68">
-        <v>2.349366269754947</v>
+        <v>2.414329390329274</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.174354880350973</v>
+        <v>2.141901822435286</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08922543265841501</v>
+        <v>0.08926965509349767</v>
       </c>
       <c r="C69">
-        <v>29.40097704211868</v>
+        <v>27.85632600719934</v>
       </c>
       <c r="D69">
-        <v>122.0179770421187</v>
+        <v>121.9143260071993</v>
       </c>
       <c r="E69">
-        <v>49.547</v>
+        <v>50.988</v>
       </c>
       <c r="F69">
-        <v>96.547</v>
+        <v>97.988</v>
       </c>
       <c r="G69">
         <v>3.93</v>
@@ -6939,28 +6939,28 @@
         <v>15.675</v>
       </c>
       <c r="M69">
-        <v>7.318262600000001</v>
+        <v>7.427490400000001</v>
       </c>
       <c r="N69">
-        <v>8.356737399999998</v>
+        <v>8.247509599999997</v>
       </c>
       <c r="O69">
-        <v>1.838482228</v>
+        <v>1.814452111999999</v>
       </c>
       <c r="P69">
-        <v>6.518255171999998</v>
+        <v>6.433057487999998</v>
       </c>
       <c r="Q69">
-        <v>11.218255172</v>
+        <v>11.133057488</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1503404626012576</v>
+        <v>0.1533291721671802</v>
       </c>
       <c r="T69">
-        <v>2.414329390329274</v>
+        <v>2.483352705939497</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.141901822435286</v>
+        <v>2.110403266223003</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08926965509349767</v>
+        <v>0.08931387752858035</v>
       </c>
       <c r="C70">
-        <v>27.85632600719934</v>
+        <v>26.31185092042622</v>
       </c>
       <c r="D70">
-        <v>121.9143260071993</v>
+        <v>121.8108509204262</v>
       </c>
       <c r="E70">
-        <v>50.988</v>
+        <v>52.429</v>
       </c>
       <c r="F70">
-        <v>97.988</v>
+        <v>99.429</v>
       </c>
       <c r="G70">
         <v>3.93</v>
@@ -7021,28 +7021,28 @@
         <v>15.675</v>
       </c>
       <c r="M70">
-        <v>7.427490400000001</v>
+        <v>7.536718200000001</v>
       </c>
       <c r="N70">
-        <v>8.247509599999997</v>
+        <v>8.138281799999998</v>
       </c>
       <c r="O70">
-        <v>1.814452111999999</v>
+        <v>1.790421996</v>
       </c>
       <c r="P70">
-        <v>6.433057487999998</v>
+        <v>6.347859803999999</v>
       </c>
       <c r="Q70">
-        <v>11.133057488</v>
+        <v>11.047859804</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1533291721671802</v>
+        <v>0.1565107017050979</v>
       </c>
       <c r="T70">
-        <v>2.483352705939497</v>
+        <v>2.556829138685864</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.110403266223003</v>
+        <v>2.079817711640061</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08931387752858035</v>
+        <v>0.08935809996366301</v>
       </c>
       <c r="C71">
-        <v>26.31185092042622</v>
+        <v>24.76755133417008</v>
       </c>
       <c r="D71">
-        <v>121.8108509204262</v>
+        <v>121.7075513341701</v>
       </c>
       <c r="E71">
-        <v>52.429</v>
+        <v>53.87</v>
       </c>
       <c r="F71">
-        <v>99.429</v>
+        <v>100.87</v>
       </c>
       <c r="G71">
         <v>3.93</v>
@@ -7103,28 +7103,28 @@
         <v>15.675</v>
       </c>
       <c r="M71">
-        <v>7.536718200000001</v>
+        <v>7.645946000000001</v>
       </c>
       <c r="N71">
-        <v>8.138281799999998</v>
+        <v>8.029053999999999</v>
       </c>
       <c r="O71">
-        <v>1.790421996</v>
+        <v>1.76639188</v>
       </c>
       <c r="P71">
-        <v>6.347859803999999</v>
+        <v>6.262662119999999</v>
       </c>
       <c r="Q71">
-        <v>11.047859804</v>
+        <v>10.96266212</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1565107017050979</v>
+        <v>0.15990433321221</v>
       </c>
       <c r="T71">
-        <v>2.556829138685864</v>
+        <v>2.635204000281987</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.079817711640061</v>
+        <v>2.050106030045203</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08935809996366301</v>
+        <v>0.08940232239874568</v>
       </c>
       <c r="C72">
-        <v>24.76755133417008</v>
+        <v>23.22342680231858</v>
       </c>
       <c r="D72">
-        <v>121.7075513341701</v>
+        <v>121.6044268023186</v>
       </c>
       <c r="E72">
-        <v>53.87</v>
+        <v>55.31100000000001</v>
       </c>
       <c r="F72">
-        <v>100.87</v>
+        <v>102.311</v>
       </c>
       <c r="G72">
         <v>3.93</v>
@@ -7185,28 +7185,28 @@
         <v>15.675</v>
       </c>
       <c r="M72">
-        <v>7.645946000000001</v>
+        <v>7.755173800000001</v>
       </c>
       <c r="N72">
-        <v>8.029053999999999</v>
+        <v>7.919826199999997</v>
       </c>
       <c r="O72">
-        <v>1.76639188</v>
+        <v>1.742361764</v>
       </c>
       <c r="P72">
-        <v>6.262662119999999</v>
+        <v>6.177464435999998</v>
       </c>
       <c r="Q72">
-        <v>10.96266212</v>
+        <v>10.877464436</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.15990433321221</v>
+        <v>0.1635320082715369</v>
       </c>
       <c r="T72">
-        <v>2.635204000281987</v>
+        <v>2.71898402474681</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.050106030045203</v>
+        <v>2.021231297227664</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0894023223987457</v>
+        <v>0.09742126483382836</v>
       </c>
       <c r="C73">
-        <v>23.22342680231857</v>
+        <v>5.586864116846897</v>
       </c>
       <c r="D73">
-        <v>121.6044268023186</v>
+        <v>105.4088641168469</v>
       </c>
       <c r="E73">
-        <v>55.31099999999999</v>
+        <v>56.752</v>
       </c>
       <c r="F73">
-        <v>102.311</v>
+        <v>103.752</v>
       </c>
       <c r="G73">
         <v>3.93</v>
@@ -7267,45 +7267,45 @@
         <v>15.675</v>
       </c>
       <c r="M73">
-        <v>7.7551738</v>
+        <v>9.337679999999999</v>
       </c>
       <c r="N73">
-        <v>7.919826199999999</v>
+        <v>6.33732</v>
       </c>
       <c r="O73">
-        <v>1.742361764</v>
+        <v>1.3942104</v>
       </c>
       <c r="P73">
-        <v>6.177464435999999</v>
+        <v>4.9431096</v>
       </c>
       <c r="Q73">
-        <v>10.877464436</v>
+        <v>9.643109600000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1635320082715368</v>
+        <v>0.1674188029779584</v>
       </c>
       <c r="T73">
-        <v>2.718984024746809</v>
+        <v>2.808748336673405</v>
       </c>
       <c r="U73">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.021231297227665</v>
+        <v>1.678682499293186</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09742126483382836</v>
+        <v>0.09757624726891104</v>
       </c>
       <c r="C74">
-        <v>5.586864116846897</v>
+        <v>3.875236117191292</v>
       </c>
       <c r="D74">
-        <v>105.4088641168469</v>
+        <v>105.1382361171913</v>
       </c>
       <c r="E74">
-        <v>56.752</v>
+        <v>58.193</v>
       </c>
       <c r="F74">
-        <v>103.752</v>
+        <v>105.193</v>
       </c>
       <c r="G74">
         <v>3.93</v>
@@ -7349,28 +7349,28 @@
         <v>15.675</v>
       </c>
       <c r="M74">
-        <v>9.337679999999999</v>
+        <v>9.467369999999999</v>
       </c>
       <c r="N74">
-        <v>6.33732</v>
+        <v>6.20763</v>
       </c>
       <c r="O74">
-        <v>1.3942104</v>
+        <v>1.3656786</v>
       </c>
       <c r="P74">
-        <v>4.9431096</v>
+        <v>4.8419514</v>
       </c>
       <c r="Q74">
-        <v>9.643109600000001</v>
+        <v>9.541951400000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1674188029779584</v>
+        <v>0.1715935084033742</v>
       </c>
       <c r="T74">
-        <v>2.808748336673405</v>
+        <v>2.905161856890859</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.678682499293186</v>
+        <v>1.655686848617937</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09757624726891104</v>
+        <v>0.0977312297039937</v>
       </c>
       <c r="C75">
-        <v>3.875236117191292</v>
+        <v>2.164994186161366</v>
       </c>
       <c r="D75">
-        <v>105.1382361171913</v>
+        <v>104.8689941861614</v>
       </c>
       <c r="E75">
-        <v>58.193</v>
+        <v>59.634</v>
       </c>
       <c r="F75">
-        <v>105.193</v>
+        <v>106.634</v>
       </c>
       <c r="G75">
         <v>3.93</v>
@@ -7431,28 +7431,28 @@
         <v>15.675</v>
       </c>
       <c r="M75">
-        <v>9.467369999999999</v>
+        <v>9.597059999999999</v>
       </c>
       <c r="N75">
-        <v>6.20763</v>
+        <v>6.07794</v>
       </c>
       <c r="O75">
-        <v>1.3656786</v>
+        <v>1.3371468</v>
       </c>
       <c r="P75">
-        <v>4.8419514</v>
+        <v>4.7407932</v>
       </c>
       <c r="Q75">
-        <v>9.541951400000002</v>
+        <v>9.440793200000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1715935084033742</v>
+        <v>0.1760893450153604</v>
       </c>
       <c r="T75">
-        <v>2.905161856890859</v>
+        <v>3.008991801740425</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.655686848617937</v>
+        <v>1.633312702014992</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0977312297039937</v>
+        <v>0.09788621213907638</v>
       </c>
       <c r="C76">
-        <v>2.164994186161366</v>
+        <v>0.456127702467171</v>
       </c>
       <c r="D76">
-        <v>104.8689941861614</v>
+        <v>104.6011277024672</v>
       </c>
       <c r="E76">
-        <v>59.634</v>
+        <v>61.07499999999999</v>
       </c>
       <c r="F76">
-        <v>106.634</v>
+        <v>108.075</v>
       </c>
       <c r="G76">
         <v>3.93</v>
@@ -7513,28 +7513,28 @@
         <v>15.675</v>
       </c>
       <c r="M76">
-        <v>9.597059999999999</v>
+        <v>9.726749999999999</v>
       </c>
       <c r="N76">
-        <v>6.07794</v>
+        <v>5.94825</v>
       </c>
       <c r="O76">
-        <v>1.3371468</v>
+        <v>1.308615</v>
       </c>
       <c r="P76">
-        <v>4.7407932</v>
+        <v>4.639635</v>
       </c>
       <c r="Q76">
-        <v>9.440793200000002</v>
+        <v>9.339635000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1760893450153604</v>
+        <v>0.1809448485563055</v>
       </c>
       <c r="T76">
-        <v>3.008991801740425</v>
+        <v>3.121128142177956</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.633312702014992</v>
+        <v>1.611535199321459</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09788621213907638</v>
+        <v>0.09804119457415905</v>
       </c>
       <c r="C77">
-        <v>0.456127702467171</v>
+        <v>-1.251373846937966</v>
       </c>
       <c r="D77">
-        <v>104.6011277024672</v>
+        <v>104.334626153062</v>
       </c>
       <c r="E77">
-        <v>61.07499999999999</v>
+        <v>62.51599999999999</v>
       </c>
       <c r="F77">
-        <v>108.075</v>
+        <v>109.516</v>
       </c>
       <c r="G77">
         <v>3.93</v>
@@ -7595,28 +7595,28 @@
         <v>15.675</v>
       </c>
       <c r="M77">
-        <v>9.726749999999999</v>
+        <v>9.856439999999999</v>
       </c>
       <c r="N77">
-        <v>5.94825</v>
+        <v>5.81856</v>
       </c>
       <c r="O77">
-        <v>1.308615</v>
+        <v>1.2800832</v>
       </c>
       <c r="P77">
-        <v>4.639635</v>
+        <v>4.5384768</v>
       </c>
       <c r="Q77">
-        <v>9.339635000000001</v>
+        <v>9.238476800000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1809448485563055</v>
+        <v>0.1862049773923294</v>
       </c>
       <c r="T77">
-        <v>3.121128142177956</v>
+        <v>3.242609177651949</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.611535199321459</v>
+        <v>1.590330788804071</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09804119457415905</v>
+        <v>0.09819617700924171</v>
       </c>
       <c r="C78">
-        <v>-1.251373846937966</v>
+        <v>-2.957520868232891</v>
       </c>
       <c r="D78">
-        <v>104.334626153062</v>
+        <v>104.0694791317671</v>
       </c>
       <c r="E78">
-        <v>62.51599999999999</v>
+        <v>63.95699999999999</v>
       </c>
       <c r="F78">
-        <v>109.516</v>
+        <v>110.957</v>
       </c>
       <c r="G78">
         <v>3.93</v>
@@ -7677,28 +7677,28 @@
         <v>15.675</v>
       </c>
       <c r="M78">
-        <v>9.856439999999999</v>
+        <v>9.986129999999999</v>
       </c>
       <c r="N78">
-        <v>5.81856</v>
+        <v>5.68887</v>
       </c>
       <c r="O78">
-        <v>1.2800832</v>
+        <v>1.2515514</v>
       </c>
       <c r="P78">
-        <v>4.5384768</v>
+        <v>4.437318599999999</v>
       </c>
       <c r="Q78">
-        <v>9.238476800000001</v>
+        <v>9.1373186</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1862049773923294</v>
+        <v>0.1919225087358336</v>
       </c>
       <c r="T78">
-        <v>3.242609177651949</v>
+        <v>3.374653781428028</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.590330788804071</v>
+        <v>1.569677142196226</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09819617700924171</v>
+        <v>0.0983511594443244</v>
       </c>
       <c r="C79">
-        <v>-2.957520868232891</v>
+        <v>-4.662323662083239</v>
       </c>
       <c r="D79">
-        <v>104.0694791317671</v>
+        <v>103.8056763379168</v>
       </c>
       <c r="E79">
-        <v>63.95699999999999</v>
+        <v>65.398</v>
       </c>
       <c r="F79">
-        <v>110.957</v>
+        <v>112.398</v>
       </c>
       <c r="G79">
         <v>3.93</v>
@@ -7759,28 +7759,28 @@
         <v>15.675</v>
       </c>
       <c r="M79">
-        <v>9.986129999999999</v>
+        <v>10.11582</v>
       </c>
       <c r="N79">
-        <v>5.68887</v>
+        <v>5.55918</v>
       </c>
       <c r="O79">
-        <v>1.2515514</v>
+        <v>1.2230196</v>
       </c>
       <c r="P79">
-        <v>4.437318599999999</v>
+        <v>4.3361604</v>
       </c>
       <c r="Q79">
-        <v>9.1373186</v>
+        <v>9.0361604</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1919225087358336</v>
+        <v>0.19815981565602</v>
       </c>
       <c r="T79">
-        <v>3.374653781428028</v>
+        <v>3.518702440092841</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.569677142196226</v>
+        <v>1.549553076270634</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0983511594443244</v>
+        <v>0.09850614187940707</v>
       </c>
       <c r="C80">
-        <v>-4.662323662083239</v>
+        <v>-6.365792424975083</v>
       </c>
       <c r="D80">
-        <v>103.8056763379168</v>
+        <v>103.5432075750249</v>
       </c>
       <c r="E80">
-        <v>65.398</v>
+        <v>66.839</v>
       </c>
       <c r="F80">
-        <v>112.398</v>
+        <v>113.839</v>
       </c>
       <c r="G80">
         <v>3.93</v>
@@ -7841,28 +7841,28 @@
         <v>15.675</v>
       </c>
       <c r="M80">
-        <v>10.11582</v>
+        <v>10.24551</v>
       </c>
       <c r="N80">
-        <v>5.55918</v>
+        <v>5.429489999999999</v>
       </c>
       <c r="O80">
-        <v>1.2230196</v>
+        <v>1.1944878</v>
       </c>
       <c r="P80">
-        <v>4.3361604</v>
+        <v>4.235002199999999</v>
       </c>
       <c r="Q80">
-        <v>9.0361604</v>
+        <v>8.9350022</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.19815981565602</v>
+        <v>0.2049911518067004</v>
       </c>
       <c r="T80">
-        <v>3.518702440092841</v>
+        <v>3.676470018630493</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.549553076270634</v>
+        <v>1.529938480368473</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09850614187940707</v>
+        <v>0.09866112431448974</v>
       </c>
       <c r="C81">
-        <v>-6.365792424975083</v>
+        <v>-8.067937250528999</v>
       </c>
       <c r="D81">
-        <v>103.5432075750249</v>
+        <v>103.282062749471</v>
       </c>
       <c r="E81">
-        <v>66.839</v>
+        <v>68.28</v>
       </c>
       <c r="F81">
-        <v>113.839</v>
+        <v>115.28</v>
       </c>
       <c r="G81">
         <v>3.93</v>
@@ -7923,28 +7923,28 @@
         <v>15.675</v>
       </c>
       <c r="M81">
-        <v>10.24551</v>
+        <v>10.3752</v>
       </c>
       <c r="N81">
-        <v>5.429489999999999</v>
+        <v>5.299799999999999</v>
       </c>
       <c r="O81">
-        <v>1.1944878</v>
+        <v>1.165956</v>
       </c>
       <c r="P81">
-        <v>4.235002199999999</v>
+        <v>4.133844</v>
       </c>
       <c r="Q81">
-        <v>8.9350022</v>
+        <v>8.833844000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2049911518067004</v>
+        <v>0.2125056215724488</v>
       </c>
       <c r="T81">
-        <v>3.676470018630493</v>
+        <v>3.850014355021911</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.529938480368473</v>
+        <v>1.510814249363868</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09866112431448974</v>
+        <v>0.1375450407914839</v>
       </c>
       <c r="C82">
-        <v>-8.067937250528999</v>
+        <v>-49.53534916091623</v>
       </c>
       <c r="D82">
-        <v>103.282062749471</v>
+        <v>63.25565083908378</v>
       </c>
       <c r="E82">
-        <v>68.28</v>
+        <v>69.721</v>
       </c>
       <c r="F82">
-        <v>115.28</v>
+        <v>116.721</v>
       </c>
       <c r="G82">
         <v>3.93</v>
@@ -8005,45 +8005,45 @@
         <v>15.675</v>
       </c>
       <c r="M82">
-        <v>10.3752</v>
+        <v>17.1346428</v>
       </c>
       <c r="N82">
-        <v>5.299799999999999</v>
+        <v>-1.459642800000003</v>
       </c>
       <c r="O82">
-        <v>1.165956</v>
+        <v>-0.3211214160000006</v>
       </c>
       <c r="P82">
-        <v>4.133844</v>
+        <v>-1.138521384000002</v>
       </c>
       <c r="Q82">
-        <v>8.833844000000001</v>
+        <v>3.561478615999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2125056215724488</v>
+        <v>0.2240438868495137</v>
       </c>
       <c r="T82">
-        <v>3.850014355021911</v>
+        <v>4.116486994215096</v>
       </c>
       <c r="U82">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.22</v>
+        <v>0.2012589372449596</v>
       </c>
       <c r="W82">
-        <v>0.0702</v>
+        <v>0.1172551880124399</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.510814249363868</v>
+        <v>0.9148133511134529</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1375450407914839</v>
+        <v>0.1385550407914839</v>
       </c>
       <c r="C83">
-        <v>-49.53534916091623</v>
+        <v>-51.60675836321137</v>
       </c>
       <c r="D83">
-        <v>63.25565083908378</v>
+        <v>62.62524163678863</v>
       </c>
       <c r="E83">
-        <v>69.721</v>
+        <v>71.16200000000001</v>
       </c>
       <c r="F83">
-        <v>116.721</v>
+        <v>118.162</v>
       </c>
       <c r="G83">
         <v>3.93</v>
@@ -8087,37 +8087,37 @@
         <v>15.675</v>
       </c>
       <c r="M83">
-        <v>17.1346428</v>
+        <v>17.3461816</v>
       </c>
       <c r="N83">
-        <v>-1.459642800000003</v>
+        <v>-1.671181600000002</v>
       </c>
       <c r="O83">
-        <v>-0.3211214160000006</v>
+        <v>-0.3676599520000005</v>
       </c>
       <c r="P83">
-        <v>-1.138521384000002</v>
+        <v>-1.303521648000002</v>
       </c>
       <c r="Q83">
-        <v>3.561478615999999</v>
+        <v>3.396478351999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2240438868495137</v>
+        <v>0.2339463250078199</v>
       </c>
       <c r="T83">
-        <v>4.116486994215096</v>
+        <v>4.345180716115934</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2012589372449596</v>
+        <v>0.1988045599614845</v>
       </c>
       <c r="W83">
-        <v>0.1172551880124399</v>
+        <v>0.1176154905976541</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9148133511134529</v>
+        <v>0.9036570907340206</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1385550407914839</v>
+        <v>0.1395650407914839</v>
       </c>
       <c r="C84">
-        <v>-51.60675836321137</v>
+        <v>-53.66572617337557</v>
       </c>
       <c r="D84">
-        <v>62.62524163678863</v>
+        <v>62.00727382662443</v>
       </c>
       <c r="E84">
-        <v>71.16200000000001</v>
+        <v>72.60300000000001</v>
       </c>
       <c r="F84">
-        <v>118.162</v>
+        <v>119.603</v>
       </c>
       <c r="G84">
         <v>3.93</v>
@@ -8169,37 +8169,37 @@
         <v>15.675</v>
       </c>
       <c r="M84">
-        <v>17.3461816</v>
+        <v>17.5577204</v>
       </c>
       <c r="N84">
-        <v>-1.671181600000002</v>
+        <v>-1.882720400000006</v>
       </c>
       <c r="O84">
-        <v>-0.3676599520000005</v>
+        <v>-0.4141984880000012</v>
       </c>
       <c r="P84">
-        <v>-1.303521648000002</v>
+        <v>-1.468521912000004</v>
       </c>
       <c r="Q84">
-        <v>3.396478351999999</v>
+        <v>3.231478087999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2339463250078199</v>
+        <v>0.2450137558906329</v>
       </c>
       <c r="T84">
-        <v>4.345180716115934</v>
+        <v>4.600779581769813</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1988045599614845</v>
+        <v>0.1964093242992979</v>
       </c>
       <c r="W84">
-        <v>0.1176154905976541</v>
+        <v>0.1179671111928631</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9036570907340206</v>
+        <v>0.8927696559058996</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1395650407914839</v>
+        <v>0.1405750407914839</v>
       </c>
       <c r="C85">
-        <v>-53.66572617337557</v>
+        <v>-55.71261729680177</v>
       </c>
       <c r="D85">
-        <v>62.00727382662443</v>
+        <v>61.40138270319824</v>
       </c>
       <c r="E85">
-        <v>72.60300000000001</v>
+        <v>74.04400000000001</v>
       </c>
       <c r="F85">
-        <v>119.603</v>
+        <v>121.044</v>
       </c>
       <c r="G85">
         <v>3.93</v>
@@ -8251,37 +8251,37 @@
         <v>15.675</v>
       </c>
       <c r="M85">
-        <v>17.5577204</v>
+        <v>17.7692592</v>
       </c>
       <c r="N85">
-        <v>-1.882720400000006</v>
+        <v>-2.094259200000005</v>
       </c>
       <c r="O85">
-        <v>-0.4141984880000012</v>
+        <v>-0.4607370240000011</v>
       </c>
       <c r="P85">
-        <v>-1.468521912000004</v>
+        <v>-1.633522176000004</v>
       </c>
       <c r="Q85">
-        <v>3.231478087999997</v>
+        <v>3.066477823999997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2450137558906329</v>
+        <v>0.2574646156337975</v>
       </c>
       <c r="T85">
-        <v>4.600779581769813</v>
+        <v>4.888328305630427</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1964093242992979</v>
+        <v>0.1940711180576396</v>
       </c>
       <c r="W85">
-        <v>0.1179671111928631</v>
+        <v>0.1183103598691385</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8927696559058996</v>
+        <v>0.8821414457165437</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1405750407914839</v>
+        <v>0.1415850407914839</v>
       </c>
       <c r="C86">
-        <v>-55.71261729680175</v>
+        <v>-57.74778232225027</v>
       </c>
       <c r="D86">
-        <v>61.40138270319824</v>
+        <v>60.8072176777497</v>
       </c>
       <c r="E86">
-        <v>74.044</v>
+        <v>75.48499999999999</v>
       </c>
       <c r="F86">
-        <v>121.044</v>
+        <v>122.485</v>
       </c>
       <c r="G86">
         <v>3.93</v>
@@ -8333,37 +8333,37 @@
         <v>15.675</v>
       </c>
       <c r="M86">
-        <v>17.7692592</v>
+        <v>17.980798</v>
       </c>
       <c r="N86">
-        <v>-2.094259200000002</v>
+        <v>-2.305798000000001</v>
       </c>
       <c r="O86">
-        <v>-0.4607370240000003</v>
+        <v>-0.5072755600000003</v>
       </c>
       <c r="P86">
-        <v>-1.633522176000001</v>
+        <v>-1.798522440000001</v>
       </c>
       <c r="Q86">
-        <v>3.066477824</v>
+        <v>2.90147756</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2574646156337974</v>
+        <v>0.2715755900093839</v>
       </c>
       <c r="T86">
-        <v>4.888328305630424</v>
+        <v>5.214216859339119</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1940711180576397</v>
+        <v>0.1917879284334321</v>
       </c>
       <c r="W86">
-        <v>0.1183103598691385</v>
+        <v>0.1186455321059722</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.882141445716544</v>
+        <v>0.8717633110610552</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1415850407914839</v>
+        <v>0.1425950407914839</v>
       </c>
       <c r="C87">
-        <v>-57.74778232225027</v>
+        <v>-59.77155839831775</v>
       </c>
       <c r="D87">
-        <v>60.8072176777497</v>
+        <v>60.22444160168223</v>
       </c>
       <c r="E87">
-        <v>75.48499999999999</v>
+        <v>76.92599999999999</v>
       </c>
       <c r="F87">
-        <v>122.485</v>
+        <v>123.926</v>
       </c>
       <c r="G87">
         <v>3.93</v>
@@ -8415,37 +8415,37 @@
         <v>15.675</v>
       </c>
       <c r="M87">
-        <v>17.980798</v>
+        <v>18.1923368</v>
       </c>
       <c r="N87">
-        <v>-2.305798000000001</v>
+        <v>-2.517336800000001</v>
       </c>
       <c r="O87">
-        <v>-0.5072755600000003</v>
+        <v>-0.5538140960000002</v>
       </c>
       <c r="P87">
-        <v>-1.798522440000001</v>
+        <v>-1.963522704000001</v>
       </c>
       <c r="Q87">
-        <v>2.90147756</v>
+        <v>2.736477296</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2715755900093839</v>
+        <v>0.287702417867197</v>
       </c>
       <c r="T87">
-        <v>5.214216859339119</v>
+        <v>5.586660920720484</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1917879284334321</v>
+        <v>0.1895578362423457</v>
       </c>
       <c r="W87">
-        <v>0.1186455321059722</v>
+        <v>0.1189729096396236</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8717633110610552</v>
+        <v>0.8616265283742988</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1425950407914839</v>
+        <v>0.1436050407914839</v>
       </c>
       <c r="C88">
-        <v>-59.77155839831775</v>
+        <v>-61.78426987137526</v>
       </c>
       <c r="D88">
-        <v>60.22444160168223</v>
+        <v>59.65273012862473</v>
       </c>
       <c r="E88">
-        <v>76.92599999999999</v>
+        <v>78.36699999999999</v>
       </c>
       <c r="F88">
-        <v>123.926</v>
+        <v>125.367</v>
       </c>
       <c r="G88">
         <v>3.93</v>
@@ -8497,37 +8497,37 @@
         <v>15.675</v>
       </c>
       <c r="M88">
-        <v>18.1923368</v>
+        <v>18.4038756</v>
       </c>
       <c r="N88">
-        <v>-2.517336800000001</v>
+        <v>-2.7288756</v>
       </c>
       <c r="O88">
-        <v>-0.5538140960000002</v>
+        <v>-0.6003526320000001</v>
       </c>
       <c r="P88">
-        <v>-1.963522704000001</v>
+        <v>-2.128522968</v>
       </c>
       <c r="Q88">
-        <v>2.736477296</v>
+        <v>2.571477032000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.287702417867197</v>
+        <v>0.3063102961646736</v>
       </c>
       <c r="T88">
-        <v>5.586660920720484</v>
+        <v>6.016404068468214</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1895578362423457</v>
+        <v>0.1873790105384107</v>
       </c>
       <c r="W88">
-        <v>0.1189729096396236</v>
+        <v>0.1192927612529613</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8616265283742988</v>
+        <v>0.8517227751745942</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1436050407914839</v>
+        <v>0.1446150407914839</v>
       </c>
       <c r="C89">
-        <v>-61.78426987137526</v>
+        <v>-63.78622888751252</v>
       </c>
       <c r="D89">
-        <v>59.65273012862473</v>
+        <v>59.09177111248747</v>
       </c>
       <c r="E89">
-        <v>78.36699999999999</v>
+        <v>79.80799999999999</v>
       </c>
       <c r="F89">
-        <v>125.367</v>
+        <v>126.808</v>
       </c>
       <c r="G89">
         <v>3.93</v>
@@ -8579,37 +8579,37 @@
         <v>15.675</v>
       </c>
       <c r="M89">
-        <v>18.4038756</v>
+        <v>18.6154144</v>
       </c>
       <c r="N89">
-        <v>-2.7288756</v>
+        <v>-2.940414400000003</v>
       </c>
       <c r="O89">
-        <v>-0.6003526320000001</v>
+        <v>-0.6468911680000008</v>
       </c>
       <c r="P89">
-        <v>-2.128522968</v>
+        <v>-2.293523232000003</v>
       </c>
       <c r="Q89">
-        <v>2.571477032000001</v>
+        <v>2.406476767999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3063102961646736</v>
+        <v>0.3280194875117299</v>
       </c>
       <c r="T89">
-        <v>6.016404068468214</v>
+        <v>6.5177710741739</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1873790105384107</v>
+        <v>0.1852497036004742</v>
       </c>
       <c r="W89">
-        <v>0.1192927612529613</v>
+        <v>0.1196053435114504</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8517227751745942</v>
+        <v>0.8420441072748828</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1446150407914839</v>
+        <v>0.1456250407914839</v>
       </c>
       <c r="C90">
-        <v>-63.78622888751252</v>
+        <v>-65.7777359608356</v>
       </c>
       <c r="D90">
-        <v>59.09177111248747</v>
+        <v>58.5412640391644</v>
       </c>
       <c r="E90">
-        <v>79.80799999999999</v>
+        <v>81.249</v>
       </c>
       <c r="F90">
-        <v>126.808</v>
+        <v>128.249</v>
       </c>
       <c r="G90">
         <v>3.93</v>
@@ -8661,37 +8661,37 @@
         <v>15.675</v>
       </c>
       <c r="M90">
-        <v>18.6154144</v>
+        <v>18.8269532</v>
       </c>
       <c r="N90">
-        <v>-2.940414400000003</v>
+        <v>-3.151953200000003</v>
       </c>
       <c r="O90">
-        <v>-0.6468911680000008</v>
+        <v>-0.6934297040000007</v>
       </c>
       <c r="P90">
-        <v>-2.293523232000003</v>
+        <v>-2.458523496000002</v>
       </c>
       <c r="Q90">
-        <v>2.406476767999998</v>
+        <v>2.241476503999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3280194875117299</v>
+        <v>0.3536758045582508</v>
       </c>
       <c r="T90">
-        <v>6.5177710741739</v>
+        <v>7.110295717280619</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1852497036004742</v>
+        <v>0.1831682462566487</v>
       </c>
       <c r="W90">
-        <v>0.1196053435114504</v>
+        <v>0.119910901449524</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8420441072748828</v>
+        <v>0.8325829375302212</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1456250407914839</v>
+        <v>0.1466350407914839</v>
       </c>
       <c r="C91">
-        <v>-65.7777359608356</v>
+        <v>-67.7590805102915</v>
       </c>
       <c r="D91">
-        <v>58.5412640391644</v>
+        <v>58.0009194897085</v>
       </c>
       <c r="E91">
-        <v>81.249</v>
+        <v>82.69</v>
       </c>
       <c r="F91">
-        <v>128.249</v>
+        <v>129.69</v>
       </c>
       <c r="G91">
         <v>3.93</v>
@@ -8743,37 +8743,37 @@
         <v>15.675</v>
       </c>
       <c r="M91">
-        <v>18.8269532</v>
+        <v>19.038492</v>
       </c>
       <c r="N91">
-        <v>-3.151953200000003</v>
+        <v>-3.363492000000003</v>
       </c>
       <c r="O91">
-        <v>-0.6934297040000007</v>
+        <v>-0.7399682400000006</v>
       </c>
       <c r="P91">
-        <v>-2.458523496000002</v>
+        <v>-2.623523760000002</v>
       </c>
       <c r="Q91">
-        <v>2.241476503999999</v>
+        <v>2.076476239999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3536758045582508</v>
+        <v>0.384463385014076</v>
       </c>
       <c r="T91">
-        <v>7.110295717280619</v>
+        <v>7.821325289008683</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1831682462566487</v>
+        <v>0.1811330435204637</v>
       </c>
       <c r="W91">
-        <v>0.119910901449524</v>
+        <v>0.1202096692111959</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8325829375302212</v>
+        <v>0.8233320160021076</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1466350407914839</v>
+        <v>0.1476450407914839</v>
       </c>
       <c r="C92">
-        <v>-67.7590805102915</v>
+        <v>-69.73054136703485</v>
       </c>
       <c r="D92">
-        <v>58.0009194897085</v>
+        <v>57.47045863296515</v>
       </c>
       <c r="E92">
-        <v>82.69</v>
+        <v>84.131</v>
       </c>
       <c r="F92">
-        <v>129.69</v>
+        <v>131.131</v>
       </c>
       <c r="G92">
         <v>3.93</v>
@@ -8825,37 +8825,37 @@
         <v>15.675</v>
       </c>
       <c r="M92">
-        <v>19.038492</v>
+        <v>19.2500308</v>
       </c>
       <c r="N92">
-        <v>-3.363492000000003</v>
+        <v>-3.575030800000002</v>
       </c>
       <c r="O92">
-        <v>-0.7399682400000006</v>
+        <v>-0.7865067760000005</v>
       </c>
       <c r="P92">
-        <v>-2.623523760000002</v>
+        <v>-2.788524024000002</v>
       </c>
       <c r="Q92">
-        <v>2.076476239999999</v>
+        <v>1.911475975999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.384463385014076</v>
+        <v>0.4220926500156399</v>
       </c>
       <c r="T92">
-        <v>7.821325289008683</v>
+        <v>8.690361432231869</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1811330435204637</v>
+        <v>0.1791425705147443</v>
       </c>
       <c r="W92">
-        <v>0.1202096692111959</v>
+        <v>0.1205018706484356</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8233320160021076</v>
+        <v>0.8142844114306559</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1476450407914839</v>
+        <v>0.1486550407914839</v>
       </c>
       <c r="C93">
-        <v>-69.73054136703485</v>
+        <v>-71.69238725420556</v>
       </c>
       <c r="D93">
-        <v>57.47045863296515</v>
+        <v>56.94961274579444</v>
       </c>
       <c r="E93">
-        <v>84.131</v>
+        <v>85.572</v>
       </c>
       <c r="F93">
-        <v>131.131</v>
+        <v>132.572</v>
       </c>
       <c r="G93">
         <v>3.93</v>
@@ -8907,37 +8907,37 @@
         <v>15.675</v>
       </c>
       <c r="M93">
-        <v>19.2500308</v>
+        <v>19.4615696</v>
       </c>
       <c r="N93">
-        <v>-3.575030800000002</v>
+        <v>-3.786569600000002</v>
       </c>
       <c r="O93">
-        <v>-0.7865067760000005</v>
+        <v>-0.8330453120000004</v>
       </c>
       <c r="P93">
-        <v>-2.788524024000002</v>
+        <v>-2.953524288000001</v>
       </c>
       <c r="Q93">
-        <v>1.911475975999999</v>
+        <v>1.746475712</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4220926500156399</v>
+        <v>0.469129231267595</v>
       </c>
       <c r="T93">
-        <v>8.690361432231869</v>
+        <v>9.776656611260854</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1791425705147443</v>
+        <v>0.1771953686613232</v>
       </c>
       <c r="W93">
-        <v>0.1205018706484356</v>
+        <v>0.1207877198805178</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8142844114306559</v>
+        <v>0.8054334939151053</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1486550407914839</v>
+        <v>0.2016589168589604</v>
       </c>
       <c r="C94">
-        <v>-71.69238725420556</v>
+        <v>-91.48904978322818</v>
       </c>
       <c r="D94">
-        <v>56.94961274579444</v>
+        <v>38.59395021677183</v>
       </c>
       <c r="E94">
-        <v>85.572</v>
+        <v>87.01300000000001</v>
       </c>
       <c r="F94">
-        <v>132.572</v>
+        <v>134.013</v>
       </c>
       <c r="G94">
         <v>3.93</v>
@@ -8989,45 +8989,45 @@
         <v>15.675</v>
       </c>
       <c r="M94">
-        <v>19.4615696</v>
+        <v>26.9098104</v>
       </c>
       <c r="N94">
-        <v>-3.786569600000002</v>
+        <v>-11.2348104</v>
       </c>
       <c r="O94">
-        <v>-0.8330453120000004</v>
+        <v>-2.471658288</v>
       </c>
       <c r="P94">
-        <v>-2.953524288000001</v>
+        <v>-8.763152112000002</v>
       </c>
       <c r="Q94">
-        <v>1.746475712</v>
+        <v>-4.063152112000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.469129231267595</v>
+        <v>0.5549459224126305</v>
       </c>
       <c r="T94">
-        <v>9.776656611260854</v>
+        <v>11.75856633747415</v>
       </c>
       <c r="U94">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1771953686613232</v>
+        <v>0.1281502897545499</v>
       </c>
       <c r="W94">
-        <v>0.1207877198805178</v>
+        <v>0.1750674218172864</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.8054334939151053</v>
+        <v>0.5825013170661357</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2016589168589604</v>
+        <v>0.2032089168589605</v>
       </c>
       <c r="C95">
-        <v>-91.48904978322818</v>
+        <v>-93.29041953282631</v>
       </c>
       <c r="D95">
-        <v>38.59395021677183</v>
+        <v>38.2335804671737</v>
       </c>
       <c r="E95">
-        <v>87.01300000000001</v>
+        <v>88.45400000000001</v>
       </c>
       <c r="F95">
-        <v>134.013</v>
+        <v>135.454</v>
       </c>
       <c r="G95">
         <v>3.93</v>
@@ -9071,37 +9071,37 @@
         <v>15.675</v>
       </c>
       <c r="M95">
-        <v>26.9098104</v>
+        <v>27.1991632</v>
       </c>
       <c r="N95">
-        <v>-11.2348104</v>
+        <v>-11.5241632</v>
       </c>
       <c r="O95">
-        <v>-2.471658288</v>
+        <v>-2.535315904</v>
       </c>
       <c r="P95">
-        <v>-8.763152112000002</v>
+        <v>-8.988847296000001</v>
       </c>
       <c r="Q95">
-        <v>-4.063152112000001</v>
+        <v>-4.288847296</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5549459224126305</v>
+        <v>0.6398035761480692</v>
       </c>
       <c r="T95">
-        <v>11.75856633747415</v>
+        <v>13.71832739371984</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1281502897545499</v>
+        <v>0.1267869887997143</v>
       </c>
       <c r="W95">
-        <v>0.1750674218172864</v>
+        <v>0.1753411726490174</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5825013170661357</v>
+        <v>0.5763044945441556</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2032089168589605</v>
+        <v>0.2047589168589605</v>
       </c>
       <c r="C96">
-        <v>-93.29041953282631</v>
+        <v>-95.08512165960173</v>
       </c>
       <c r="D96">
-        <v>38.2335804671737</v>
+        <v>37.87987834039829</v>
       </c>
       <c r="E96">
-        <v>88.45400000000001</v>
+        <v>89.89500000000001</v>
       </c>
       <c r="F96">
-        <v>135.454</v>
+        <v>136.895</v>
       </c>
       <c r="G96">
         <v>3.93</v>
@@ -9153,37 +9153,37 @@
         <v>15.675</v>
       </c>
       <c r="M96">
-        <v>27.1991632</v>
+        <v>27.488516</v>
       </c>
       <c r="N96">
-        <v>-11.5241632</v>
+        <v>-11.81351600000001</v>
       </c>
       <c r="O96">
-        <v>-2.535315904</v>
+        <v>-2.598973520000001</v>
       </c>
       <c r="P96">
-        <v>-8.988847296000001</v>
+        <v>-9.214542480000004</v>
       </c>
       <c r="Q96">
-        <v>-4.288847296</v>
+        <v>-4.514542480000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6398035761480692</v>
+        <v>0.7586042913776834</v>
       </c>
       <c r="T96">
-        <v>13.71832739371984</v>
+        <v>16.46199287246382</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1267869887997143</v>
+        <v>0.125452388917612</v>
       </c>
       <c r="W96">
-        <v>0.1753411726490174</v>
+        <v>0.1756091603053435</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5763044945441556</v>
+        <v>0.5702381314436908</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2047589168589605</v>
+        <v>0.2063089168589605</v>
       </c>
       <c r="C97">
-        <v>-95.08512165960173</v>
+        <v>-96.87333951559799</v>
       </c>
       <c r="D97">
-        <v>37.87987834039829</v>
+        <v>37.53266048440203</v>
       </c>
       <c r="E97">
-        <v>89.89500000000001</v>
+        <v>91.33600000000001</v>
       </c>
       <c r="F97">
-        <v>136.895</v>
+        <v>138.336</v>
       </c>
       <c r="G97">
         <v>3.93</v>
@@ -9235,37 +9235,37 @@
         <v>15.675</v>
       </c>
       <c r="M97">
-        <v>27.488516</v>
+        <v>27.7778688</v>
       </c>
       <c r="N97">
-        <v>-11.81351600000001</v>
+        <v>-12.1028688</v>
       </c>
       <c r="O97">
-        <v>-2.598973520000001</v>
+        <v>-2.662631136000001</v>
       </c>
       <c r="P97">
-        <v>-9.214542480000004</v>
+        <v>-9.440237664000003</v>
       </c>
       <c r="Q97">
-        <v>-4.514542480000003</v>
+        <v>-4.740237664000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7586042913776834</v>
+        <v>0.9368053642221047</v>
       </c>
       <c r="T97">
-        <v>16.46199287246382</v>
+        <v>20.57749109057979</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.125452388917612</v>
+        <v>0.1241455931997202</v>
       </c>
       <c r="W97">
-        <v>0.1756091603053435</v>
+        <v>0.1758715648854962</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5702381314436908</v>
+        <v>0.564298150907819</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2063089168589605</v>
+        <v>0.2078589168589605</v>
       </c>
       <c r="C98">
-        <v>-96.87333951559796</v>
+        <v>-98.65524979129026</v>
       </c>
       <c r="D98">
-        <v>37.53266048440203</v>
+        <v>37.19175020870972</v>
       </c>
       <c r="E98">
-        <v>91.33599999999998</v>
+        <v>92.77699999999999</v>
       </c>
       <c r="F98">
-        <v>138.336</v>
+        <v>139.777</v>
       </c>
       <c r="G98">
         <v>3.93</v>
@@ -9317,37 +9317,37 @@
         <v>15.675</v>
       </c>
       <c r="M98">
-        <v>27.7778688</v>
+        <v>28.0672216</v>
       </c>
       <c r="N98">
-        <v>-12.1028688</v>
+        <v>-12.3922216</v>
       </c>
       <c r="O98">
-        <v>-2.662631135999999</v>
+        <v>-2.726288752</v>
       </c>
       <c r="P98">
-        <v>-9.440237663999998</v>
+        <v>-9.665932848000001</v>
       </c>
       <c r="Q98">
-        <v>-4.740237663999997</v>
+        <v>-4.965932848</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9368053642221023</v>
+        <v>1.233807152296136</v>
       </c>
       <c r="T98">
-        <v>20.57749109057973</v>
+        <v>27.43665478743964</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1241455931997202</v>
+        <v>0.1228657417234344</v>
       </c>
       <c r="W98">
-        <v>0.1758715648854962</v>
+        <v>0.1761285590619344</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5642981509078191</v>
+        <v>0.5584806441974292</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2078589168589605</v>
+        <v>0.2094089168589605</v>
       </c>
       <c r="C99">
-        <v>-98.65524979129026</v>
+        <v>-100.4310228153984</v>
       </c>
       <c r="D99">
-        <v>37.19175020870972</v>
+        <v>36.85697718460157</v>
       </c>
       <c r="E99">
-        <v>92.77699999999999</v>
+        <v>94.21799999999999</v>
       </c>
       <c r="F99">
-        <v>139.777</v>
+        <v>141.218</v>
       </c>
       <c r="G99">
         <v>3.93</v>
@@ -9399,37 +9399,37 @@
         <v>15.675</v>
       </c>
       <c r="M99">
-        <v>28.0672216</v>
+        <v>28.3565744</v>
       </c>
       <c r="N99">
-        <v>-12.3922216</v>
+        <v>-12.6815744</v>
       </c>
       <c r="O99">
-        <v>-2.726288752</v>
+        <v>-2.789946368</v>
       </c>
       <c r="P99">
-        <v>-9.665932848000001</v>
+        <v>-9.891628032</v>
       </c>
       <c r="Q99">
-        <v>-4.965932848</v>
+        <v>-5.191628031999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.233807152296136</v>
+        <v>1.827810728444205</v>
       </c>
       <c r="T99">
-        <v>27.43665478743964</v>
+        <v>41.15498218115946</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1228657417234344</v>
+        <v>0.121612009665032</v>
       </c>
       <c r="W99">
-        <v>0.1761285590619344</v>
+        <v>0.1763803084592616</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5584806441974292</v>
+        <v>0.5527818621137819</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2094089168589605</v>
+        <v>0.2109589168589605</v>
       </c>
       <c r="C100">
-        <v>-100.4310228153984</v>
+        <v>-102.2008228386519</v>
       </c>
       <c r="D100">
-        <v>36.85697718460157</v>
+        <v>36.52817716134805</v>
       </c>
       <c r="E100">
-        <v>94.21799999999999</v>
+        <v>95.65899999999999</v>
       </c>
       <c r="F100">
-        <v>141.218</v>
+        <v>142.659</v>
       </c>
       <c r="G100">
         <v>3.93</v>
@@ -9481,37 +9481,37 @@
         <v>15.675</v>
       </c>
       <c r="M100">
-        <v>28.3565744</v>
+        <v>28.6459272</v>
       </c>
       <c r="N100">
-        <v>-12.6815744</v>
+        <v>-12.9709272</v>
       </c>
       <c r="O100">
-        <v>-2.789946368</v>
+        <v>-2.853603984</v>
       </c>
       <c r="P100">
-        <v>-9.891628032</v>
+        <v>-10.117323216</v>
       </c>
       <c r="Q100">
-        <v>-5.191628031999999</v>
+        <v>-5.417323215999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.827810728444205</v>
+        <v>3.609821456888409</v>
       </c>
       <c r="T100">
-        <v>41.15498218115946</v>
+        <v>82.30996436231892</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.121612009665032</v>
+        <v>0.1203836055270014</v>
       </c>
       <c r="W100">
-        <v>0.1763803084592616</v>
+        <v>0.1766269720101781</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5527818621137819</v>
+        <v>0.5471982069409155</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2109589168589605</v>
-      </c>
-      <c r="C101">
-        <v>-102.2008228386519</v>
-      </c>
-      <c r="D101">
-        <v>36.52817716134805</v>
-      </c>
-      <c r="E101">
-        <v>95.65899999999999</v>
-      </c>
-      <c r="F101">
-        <v>142.659</v>
-      </c>
-      <c r="G101">
-        <v>3.93</v>
-      </c>
-      <c r="H101">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20.375</v>
-      </c>
-      <c r="K101">
-        <v>4.700000000000001</v>
-      </c>
-      <c r="L101">
-        <v>15.675</v>
-      </c>
-      <c r="M101">
-        <v>28.6459272</v>
-      </c>
-      <c r="N101">
-        <v>-12.9709272</v>
-      </c>
-      <c r="O101">
-        <v>-2.853603984</v>
-      </c>
-      <c r="P101">
-        <v>-10.117323216</v>
-      </c>
-      <c r="Q101">
-        <v>-5.417323215999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.609821456888409</v>
-      </c>
-      <c r="T101">
-        <v>82.30996436231892</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1203836055270014</v>
-      </c>
-      <c r="W101">
-        <v>0.1766269720101781</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5471982069409155</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
